--- a/research/traditional_assets/database/data/thailand/thailand_office_equipment_services.xlsx
+++ b/research/traditional_assets/database/data/thailand/thailand_office_equipment_services.xlsx
@@ -1540,7 +1540,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1677,22 +1677,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.0954795273772575</v>
+        <v>0.09532456832250298</v>
       </c>
       <c r="C2">
-        <v>13.61485758943439</v>
+        <v>13.50674762644546</v>
       </c>
       <c r="D2">
-        <v>11.45485758943439</v>
+        <v>11.48014762644546</v>
       </c>
       <c r="E2">
-        <v>-7.28</v>
+        <v>-7.1466</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.1334</v>
       </c>
       <c r="G2">
         <v>2.16</v>
@@ -1713,28 +1713,28 @@
         <v>2.12</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.006710019999999999</v>
       </c>
       <c r="N2">
-        <v>2.12</v>
+        <v>2.11328998</v>
       </c>
       <c r="O2">
-        <v>0.424</v>
+        <v>0.4226579960000001</v>
       </c>
       <c r="P2">
-        <v>1.696</v>
+        <v>1.690631984</v>
       </c>
       <c r="Q2">
-        <v>2.276</v>
+        <v>2.270631984</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.0954795273772575</v>
+        <v>0.09588097810353836</v>
       </c>
       <c r="T2">
-        <v>0.7685264885431575</v>
+        <v>0.7747368036020922</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>315.945407018161</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1759,22 +1759,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09532456832250298</v>
+        <v>0.09516960926774846</v>
       </c>
       <c r="C3">
-        <v>13.50674762644546</v>
+        <v>13.39874958124678</v>
       </c>
       <c r="D3">
-        <v>11.48014762644546</v>
+        <v>11.50554958124678</v>
       </c>
       <c r="E3">
-        <v>-7.1466</v>
+        <v>-7.0132</v>
       </c>
       <c r="F3">
-        <v>0.1334</v>
+        <v>0.2668</v>
       </c>
       <c r="G3">
         <v>2.16</v>
@@ -1795,28 +1795,28 @@
         <v>2.12</v>
       </c>
       <c r="M3">
-        <v>0.006710019999999999</v>
+        <v>0.01342004</v>
       </c>
       <c r="N3">
-        <v>2.11328998</v>
+        <v>2.10657996</v>
       </c>
       <c r="O3">
-        <v>0.4226579960000001</v>
+        <v>0.421315992</v>
       </c>
       <c r="P3">
-        <v>1.690631984</v>
+        <v>1.685263968</v>
       </c>
       <c r="Q3">
-        <v>2.270631984</v>
+        <v>2.265263968</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09588097810353836</v>
+        <v>0.09629062170178415</v>
       </c>
       <c r="T3">
-        <v>0.7747368036020922</v>
+        <v>0.7810738597846785</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1833,7 +1833,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>315.945407018161</v>
+        <v>157.9727035090805</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1841,22 +1841,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09516960926774846</v>
+        <v>0.09501465021299396</v>
       </c>
       <c r="C4">
-        <v>13.39874958124678</v>
+        <v>13.29086419840241</v>
       </c>
       <c r="D4">
-        <v>11.50554958124678</v>
+        <v>11.53106419840241</v>
       </c>
       <c r="E4">
-        <v>-7.0132</v>
+        <v>-6.8798</v>
       </c>
       <c r="F4">
-        <v>0.2668</v>
+        <v>0.4002</v>
       </c>
       <c r="G4">
         <v>2.16</v>
@@ -1877,28 +1877,28 @@
         <v>2.12</v>
       </c>
       <c r="M4">
-        <v>0.01342004</v>
+        <v>0.02013006</v>
       </c>
       <c r="N4">
-        <v>2.10657996</v>
+        <v>2.09986994</v>
       </c>
       <c r="O4">
-        <v>0.421315992</v>
+        <v>0.419973988</v>
       </c>
       <c r="P4">
-        <v>1.685263968</v>
+        <v>1.679895952</v>
       </c>
       <c r="Q4">
-        <v>2.265263968</v>
+        <v>2.259895952</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09629062170178415</v>
+        <v>0.09670871155978758</v>
       </c>
       <c r="T4">
-        <v>0.7810738597846785</v>
+        <v>0.787541576919483</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>157.9727035090805</v>
+        <v>105.3151356727203</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1923,22 +1923,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09501465021299396</v>
+        <v>0.09485969115823943</v>
       </c>
       <c r="C5">
-        <v>13.29086419840241</v>
+        <v>13.18309222909566</v>
       </c>
       <c r="D5">
-        <v>11.53106419840241</v>
+        <v>11.55669222909566</v>
       </c>
       <c r="E5">
-        <v>-6.8798</v>
+        <v>-6.7464</v>
       </c>
       <c r="F5">
-        <v>0.4002</v>
+        <v>0.5336</v>
       </c>
       <c r="G5">
         <v>2.16</v>
@@ -1959,28 +1959,28 @@
         <v>2.12</v>
       </c>
       <c r="M5">
-        <v>0.02013006</v>
+        <v>0.02684008</v>
       </c>
       <c r="N5">
-        <v>2.09986994</v>
+        <v>2.09315992</v>
       </c>
       <c r="O5">
-        <v>0.419973988</v>
+        <v>0.4186319840000001</v>
       </c>
       <c r="P5">
-        <v>1.679895952</v>
+        <v>1.674527936</v>
       </c>
       <c r="Q5">
-        <v>2.259895952</v>
+        <v>2.254527936</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09670871155978758</v>
+        <v>0.09713551162316608</v>
       </c>
       <c r="T5">
-        <v>0.787541576919483</v>
+        <v>0.7941440381612629</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>105.3151356727203</v>
+        <v>78.98635175454025</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -2005,22 +2005,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09485969115823943</v>
+        <v>0.09470473210348491</v>
       </c>
       <c r="C6">
-        <v>13.18309222909566</v>
+        <v>13.07543443120277</v>
       </c>
       <c r="D6">
-        <v>11.55669222909566</v>
+        <v>11.58243443120277</v>
       </c>
       <c r="E6">
-        <v>-6.7464</v>
+        <v>-6.613</v>
       </c>
       <c r="F6">
-        <v>0.5336</v>
+        <v>0.667</v>
       </c>
       <c r="G6">
         <v>2.16</v>
@@ -2041,28 +2041,28 @@
         <v>2.12</v>
       </c>
       <c r="M6">
-        <v>0.02684008</v>
+        <v>0.0335501</v>
       </c>
       <c r="N6">
-        <v>2.09315992</v>
+        <v>2.0864499</v>
       </c>
       <c r="O6">
-        <v>0.4186319840000001</v>
+        <v>0.4172899800000001</v>
       </c>
       <c r="P6">
-        <v>1.674527936</v>
+        <v>1.66915992</v>
       </c>
       <c r="Q6">
-        <v>2.254527936</v>
+        <v>2.24915992</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09713551162316608</v>
+        <v>0.09757129695103675</v>
       </c>
       <c r="T6">
-        <v>0.7941440381612629</v>
+        <v>0.8008854985870799</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>78.98635175454025</v>
+        <v>63.18908140363219</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2087,22 +2087,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09470473210348491</v>
+        <v>0.09454977304873041</v>
       </c>
       <c r="C7">
-        <v>13.07543443120277</v>
+        <v>12.96789156936767</v>
       </c>
       <c r="D7">
-        <v>11.58243443120277</v>
+        <v>11.60829156936767</v>
       </c>
       <c r="E7">
-        <v>-6.613</v>
+        <v>-6.4796</v>
       </c>
       <c r="F7">
-        <v>0.667</v>
+        <v>0.8004</v>
       </c>
       <c r="G7">
         <v>2.16</v>
@@ -2123,28 +2123,28 @@
         <v>2.12</v>
       </c>
       <c r="M7">
-        <v>0.0335501</v>
+        <v>0.04026012</v>
       </c>
       <c r="N7">
-        <v>2.0864499</v>
+        <v>2.07973988</v>
       </c>
       <c r="O7">
-        <v>0.4172899800000001</v>
+        <v>0.415947976</v>
       </c>
       <c r="P7">
-        <v>1.66915992</v>
+        <v>1.663791904</v>
       </c>
       <c r="Q7">
-        <v>2.24915992</v>
+        <v>2.243791904</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09757129695103675</v>
+        <v>0.09801635430716002</v>
       </c>
       <c r="T7">
-        <v>0.8008854985870799</v>
+        <v>0.8077703943411061</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2161,7 +2161,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>63.18908140363219</v>
+        <v>52.65756783636015</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2169,22 +2169,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09454977304873041</v>
+        <v>0.0943948139939759</v>
       </c>
       <c r="C8">
-        <v>12.96789156936767</v>
+        <v>12.86046441507766</v>
       </c>
       <c r="D8">
-        <v>11.60829156936767</v>
+        <v>11.63426441507766</v>
       </c>
       <c r="E8">
-        <v>-6.4796</v>
+        <v>-6.346200000000001</v>
       </c>
       <c r="F8">
-        <v>0.8004</v>
+        <v>0.9337999999999999</v>
       </c>
       <c r="G8">
         <v>2.16</v>
@@ -2205,28 +2205,28 @@
         <v>2.12</v>
       </c>
       <c r="M8">
-        <v>0.04026012</v>
+        <v>0.04697013999999999</v>
       </c>
       <c r="N8">
-        <v>2.07973988</v>
+        <v>2.07302986</v>
       </c>
       <c r="O8">
-        <v>0.415947976</v>
+        <v>0.414605972</v>
       </c>
       <c r="P8">
-        <v>1.663791904</v>
+        <v>1.658423888</v>
       </c>
       <c r="Q8">
-        <v>2.243791904</v>
+        <v>2.238423888</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09801635430716002</v>
+        <v>0.0984709827892214</v>
       </c>
       <c r="T8">
-        <v>0.8077703943411061</v>
+        <v>0.8148033523694123</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2243,7 +2243,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>52.65756783636015</v>
+        <v>45.13505814545157</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2251,22 +2251,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09439481399397588</v>
+        <v>0.09423985493922139</v>
       </c>
       <c r="C9">
-        <v>12.86046441507766</v>
+        <v>12.75315374674013</v>
       </c>
       <c r="D9">
-        <v>11.63426441507766</v>
+        <v>11.66035374674013</v>
       </c>
       <c r="E9">
-        <v>-6.346200000000001</v>
+        <v>-6.212800000000001</v>
       </c>
       <c r="F9">
-        <v>0.9338000000000001</v>
+        <v>1.0672</v>
       </c>
       <c r="G9">
         <v>2.16</v>
@@ -2287,28 +2287,28 @@
         <v>2.12</v>
       </c>
       <c r="M9">
-        <v>0.04697014</v>
+        <v>0.05368015999999999</v>
       </c>
       <c r="N9">
-        <v>2.07302986</v>
+        <v>2.06631984</v>
       </c>
       <c r="O9">
-        <v>0.414605972</v>
+        <v>0.4132639680000001</v>
       </c>
       <c r="P9">
-        <v>1.658423888</v>
+        <v>1.653055872</v>
       </c>
       <c r="Q9">
-        <v>2.238423888</v>
+        <v>2.233055872</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0984709827892214</v>
+        <v>0.09893549449915368</v>
       </c>
       <c r="T9">
-        <v>0.8148033523694123</v>
+        <v>0.8219892007896381</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2325,7 +2325,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>45.13505814545156</v>
+        <v>39.49317587727013</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2333,22 +2333,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09423985493922139</v>
+        <v>0.09408489588446686</v>
       </c>
       <c r="C10">
-        <v>12.75315374674013</v>
+        <v>12.64596034976037</v>
       </c>
       <c r="D10">
-        <v>11.66035374674013</v>
+        <v>11.68656034976037</v>
       </c>
       <c r="E10">
-        <v>-6.212800000000001</v>
+        <v>-6.079400000000001</v>
       </c>
       <c r="F10">
-        <v>1.0672</v>
+        <v>1.2006</v>
       </c>
       <c r="G10">
         <v>2.16</v>
@@ -2369,28 +2369,28 @@
         <v>2.12</v>
       </c>
       <c r="M10">
-        <v>0.05368015999999999</v>
+        <v>0.06039017999999999</v>
       </c>
       <c r="N10">
-        <v>2.06631984</v>
+        <v>2.05960982</v>
       </c>
       <c r="O10">
-        <v>0.4132639680000001</v>
+        <v>0.411921964</v>
       </c>
       <c r="P10">
-        <v>1.653055872</v>
+        <v>1.647687856</v>
       </c>
       <c r="Q10">
-        <v>2.233055872</v>
+        <v>2.227687856</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09893549449915368</v>
+        <v>0.09941021525765589</v>
       </c>
       <c r="T10">
-        <v>0.8219892007896381</v>
+        <v>0.8293329799443744</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2407,7 +2407,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>39.49317587727013</v>
+        <v>35.1050452242401</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2415,22 +2415,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09408489588446686</v>
+        <v>0.09392993682971235</v>
       </c>
       <c r="C11">
-        <v>12.64596034976037</v>
+        <v>12.53888501662034</v>
       </c>
       <c r="D11">
-        <v>11.68656034976037</v>
+        <v>11.71288501662034</v>
       </c>
       <c r="E11">
-        <v>-6.079400000000001</v>
+        <v>-5.946000000000001</v>
       </c>
       <c r="F11">
-        <v>1.2006</v>
+        <v>1.334</v>
       </c>
       <c r="G11">
         <v>2.16</v>
@@ -2451,28 +2451,28 @@
         <v>2.12</v>
       </c>
       <c r="M11">
-        <v>0.06039017999999999</v>
+        <v>0.06710019999999998</v>
       </c>
       <c r="N11">
-        <v>2.05960982</v>
+        <v>2.0528998</v>
       </c>
       <c r="O11">
-        <v>0.411921964</v>
+        <v>0.41057996</v>
       </c>
       <c r="P11">
-        <v>1.647687856</v>
+        <v>1.64231984</v>
       </c>
       <c r="Q11">
-        <v>2.227687856</v>
+        <v>2.22231984</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09941021525765589</v>
+        <v>0.09989548536634704</v>
       </c>
       <c r="T11">
-        <v>0.8293329799443744</v>
+        <v>0.8368399541914381</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2489,7 +2489,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>35.1050452242401</v>
+        <v>31.5945407018161</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09392993682971235</v>
+        <v>0.09377497777495783</v>
       </c>
       <c r="C12">
-        <v>12.53888501662034</v>
+        <v>12.43192854695856</v>
       </c>
       <c r="D12">
-        <v>11.71288501662034</v>
+        <v>11.73932854695856</v>
       </c>
       <c r="E12">
-        <v>-5.946</v>
+        <v>-5.8126</v>
       </c>
       <c r="F12">
-        <v>1.334</v>
+        <v>1.4674</v>
       </c>
       <c r="G12">
         <v>2.16</v>
@@ -2533,28 +2533,28 @@
         <v>2.12</v>
       </c>
       <c r="M12">
-        <v>0.0671002</v>
+        <v>0.07381022</v>
       </c>
       <c r="N12">
-        <v>2.0528998</v>
+        <v>2.04618978</v>
       </c>
       <c r="O12">
-        <v>0.41057996</v>
+        <v>0.4092379560000001</v>
       </c>
       <c r="P12">
-        <v>1.64231984</v>
+        <v>1.636951824</v>
       </c>
       <c r="Q12">
-        <v>2.22231984</v>
+        <v>2.216951824</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09989548536634706</v>
+        <v>0.1003916604213009</v>
       </c>
       <c r="T12">
-        <v>0.8368399541914383</v>
+        <v>0.8445156244889978</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>31.59454070181609</v>
+        <v>28.72230972892372</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2579,22 +2579,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09377497777495783</v>
+        <v>0.09362001872020331</v>
       </c>
       <c r="C13">
-        <v>12.43192854695856</v>
+        <v>12.32509174765111</v>
       </c>
       <c r="D13">
-        <v>11.73932854695856</v>
+        <v>11.76589174765111</v>
       </c>
       <c r="E13">
-        <v>-5.8126</v>
+        <v>-5.6792</v>
       </c>
       <c r="F13">
-        <v>1.4674</v>
+        <v>1.6008</v>
       </c>
       <c r="G13">
         <v>2.16</v>
@@ -2615,28 +2615,28 @@
         <v>2.12</v>
       </c>
       <c r="M13">
-        <v>0.07381022</v>
+        <v>0.08052023999999999</v>
       </c>
       <c r="N13">
-        <v>2.04618978</v>
+        <v>2.03947976</v>
       </c>
       <c r="O13">
-        <v>0.4092379560000001</v>
+        <v>0.4078959520000001</v>
       </c>
       <c r="P13">
-        <v>1.636951824</v>
+        <v>1.631583808</v>
       </c>
       <c r="Q13">
-        <v>2.216951824</v>
+        <v>2.211583808</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1003916604213009</v>
+        <v>0.1008991121820492</v>
       </c>
       <c r="T13">
-        <v>0.8445156244889978</v>
+        <v>0.8523657418387748</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>28.72230972892372</v>
+        <v>26.32878391818008</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2661,22 +2661,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09362001872020331</v>
+        <v>0.0934650596654488</v>
       </c>
       <c r="C14">
-        <v>12.32509174765111</v>
+        <v>12.21837543289366</v>
       </c>
       <c r="D14">
-        <v>11.76589174765111</v>
+        <v>11.79257543289366</v>
       </c>
       <c r="E14">
-        <v>-5.6792</v>
+        <v>-5.5458</v>
       </c>
       <c r="F14">
-        <v>1.6008</v>
+        <v>1.7342</v>
       </c>
       <c r="G14">
         <v>2.16</v>
@@ -2697,28 +2697,28 @@
         <v>2.12</v>
       </c>
       <c r="M14">
-        <v>0.08052023999999999</v>
+        <v>0.08723025999999999</v>
       </c>
       <c r="N14">
-        <v>2.03947976</v>
+        <v>2.03276974</v>
       </c>
       <c r="O14">
-        <v>0.4078959520000001</v>
+        <v>0.406553948</v>
       </c>
       <c r="P14">
-        <v>1.631583808</v>
+        <v>1.626215792</v>
       </c>
       <c r="Q14">
-        <v>2.211583808</v>
+        <v>2.206215792</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1008991121820492</v>
+        <v>0.1014182295005158</v>
       </c>
       <c r="T14">
-        <v>0.8523657418387748</v>
+        <v>0.8603963216563625</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2735,7 +2735,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>26.32878391818008</v>
+        <v>24.30349284755084</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2743,22 +2743,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.0934650596654488</v>
+        <v>0.09331010061069429</v>
       </c>
       <c r="C15">
-        <v>12.21837543289366</v>
+        <v>12.1117804242847</v>
       </c>
       <c r="D15">
-        <v>11.79257543289366</v>
+        <v>11.8193804242847</v>
       </c>
       <c r="E15">
-        <v>-5.5458</v>
+        <v>-5.4124</v>
       </c>
       <c r="F15">
-        <v>1.7342</v>
+        <v>1.8676</v>
       </c>
       <c r="G15">
         <v>2.16</v>
@@ -2779,28 +2779,28 @@
         <v>2.12</v>
       </c>
       <c r="M15">
-        <v>0.08723025999999999</v>
+        <v>0.09394028</v>
       </c>
       <c r="N15">
-        <v>2.03276974</v>
+        <v>2.02605972</v>
       </c>
       <c r="O15">
-        <v>0.406553948</v>
+        <v>0.405211944</v>
       </c>
       <c r="P15">
-        <v>1.626215792</v>
+        <v>1.620847776</v>
       </c>
       <c r="Q15">
-        <v>2.206215792</v>
+        <v>2.200847776</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1014182295005158</v>
+        <v>0.1019494193147608</v>
       </c>
       <c r="T15">
-        <v>0.8603963216563625</v>
+        <v>0.8686136591441269</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2817,7 +2817,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>24.30349284755084</v>
+        <v>22.56752907272578</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2825,22 +2825,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09331010061069429</v>
+        <v>0.09315514155593976</v>
       </c>
       <c r="C16">
-        <v>12.1117804242847</v>
+        <v>12.00530755090981</v>
       </c>
       <c r="D16">
-        <v>11.8193804242847</v>
+        <v>11.84630755090981</v>
       </c>
       <c r="E16">
-        <v>-5.4124</v>
+        <v>-5.279</v>
       </c>
       <c r="F16">
-        <v>1.8676</v>
+        <v>2.001</v>
       </c>
       <c r="G16">
         <v>2.16</v>
@@ -2861,28 +2861,28 @@
         <v>2.12</v>
       </c>
       <c r="M16">
-        <v>0.09394028</v>
+        <v>0.1006503</v>
       </c>
       <c r="N16">
-        <v>2.02605972</v>
+        <v>2.0193497</v>
       </c>
       <c r="O16">
-        <v>0.405211944</v>
+        <v>0.4038699400000001</v>
       </c>
       <c r="P16">
-        <v>1.620847776</v>
+        <v>1.61547976</v>
       </c>
       <c r="Q16">
-        <v>2.200847776</v>
+        <v>2.19547976</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1019494193147608</v>
+        <v>0.1024931077128703</v>
       </c>
       <c r="T16">
-        <v>0.8686136591441269</v>
+        <v>0.8770243457492503</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2899,7 +2899,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>22.56752907272578</v>
+        <v>21.06302713454406</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2907,22 +2907,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09315514155593976</v>
+        <v>0.09300018250118526</v>
       </c>
       <c r="C17">
-        <v>12.00530755090981</v>
+        <v>11.89895764942719</v>
       </c>
       <c r="D17">
-        <v>11.84630755090981</v>
+        <v>11.87335764942719</v>
       </c>
       <c r="E17">
-        <v>-5.279</v>
+        <v>-5.1456</v>
       </c>
       <c r="F17">
-        <v>2.001</v>
+        <v>2.1344</v>
       </c>
       <c r="G17">
         <v>2.16</v>
@@ -2943,28 +2943,28 @@
         <v>2.12</v>
       </c>
       <c r="M17">
-        <v>0.1006503</v>
+        <v>0.10736032</v>
       </c>
       <c r="N17">
-        <v>2.0193497</v>
+        <v>2.01263968</v>
       </c>
       <c r="O17">
-        <v>0.4038699400000001</v>
+        <v>0.402527936</v>
       </c>
       <c r="P17">
-        <v>1.61547976</v>
+        <v>1.610111744</v>
       </c>
       <c r="Q17">
-        <v>2.19547976</v>
+        <v>2.190111744</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1024931077128703</v>
+        <v>0.1030497410728396</v>
       </c>
       <c r="T17">
-        <v>0.8770243457492503</v>
+        <v>0.8856352867973529</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>21.06302713454406</v>
+        <v>19.74658793863506</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2989,22 +2989,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09300018250118526</v>
+        <v>0.09284522344643073</v>
       </c>
       <c r="C18">
-        <v>11.89895764942719</v>
+        <v>11.79273156415431</v>
       </c>
       <c r="D18">
-        <v>11.87335764942719</v>
+        <v>11.90053156415431</v>
       </c>
       <c r="E18">
-        <v>-5.1456</v>
+        <v>-5.0122</v>
       </c>
       <c r="F18">
-        <v>2.1344</v>
+        <v>2.2678</v>
       </c>
       <c r="G18">
         <v>2.16</v>
@@ -3025,28 +3025,28 @@
         <v>2.12</v>
       </c>
       <c r="M18">
-        <v>0.10736032</v>
+        <v>0.11407034</v>
       </c>
       <c r="N18">
-        <v>2.01263968</v>
+        <v>2.00592966</v>
       </c>
       <c r="O18">
-        <v>0.402527936</v>
+        <v>0.401185932</v>
       </c>
       <c r="P18">
-        <v>1.610111744</v>
+        <v>1.604743728</v>
       </c>
       <c r="Q18">
-        <v>2.190111744</v>
+        <v>2.184743728</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1030497410728396</v>
+        <v>0.1036197872848563</v>
       </c>
       <c r="T18">
-        <v>0.8856352867973529</v>
+        <v>0.8944537204008315</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -3063,7 +3063,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>19.74658793863506</v>
+        <v>18.58502394224476</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3071,22 +3071,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09284522344643073</v>
+        <v>0.09269026439167624</v>
       </c>
       <c r="C19">
-        <v>11.79273156415431</v>
+        <v>11.68663014715572</v>
       </c>
       <c r="D19">
-        <v>11.90053156415431</v>
+        <v>11.92783014715572</v>
       </c>
       <c r="E19">
-        <v>-5.0122</v>
+        <v>-4.8788</v>
       </c>
       <c r="F19">
-        <v>2.2678</v>
+        <v>2.4012</v>
       </c>
       <c r="G19">
         <v>2.16</v>
@@ -3107,28 +3107,28 @@
         <v>2.12</v>
       </c>
       <c r="M19">
-        <v>0.11407034</v>
+        <v>0.12078036</v>
       </c>
       <c r="N19">
-        <v>2.00592966</v>
+        <v>1.99921964</v>
       </c>
       <c r="O19">
-        <v>0.401185932</v>
+        <v>0.3998439280000001</v>
       </c>
       <c r="P19">
-        <v>1.604743728</v>
+        <v>1.599375712</v>
       </c>
       <c r="Q19">
-        <v>2.184743728</v>
+        <v>2.179375712</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1036197872848563</v>
+        <v>0.1042037370630198</v>
       </c>
       <c r="T19">
-        <v>0.8944537204008315</v>
+        <v>0.9034872377507366</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -3145,7 +3145,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>18.58502394224476</v>
+        <v>17.55252261212005</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3153,22 +3153,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09269026439167623</v>
+        <v>0.09253530533692172</v>
       </c>
       <c r="C20">
-        <v>11.68663014715572</v>
+        <v>11.58065425833215</v>
       </c>
       <c r="D20">
-        <v>11.92783014715572</v>
+        <v>11.95525425833215</v>
       </c>
       <c r="E20">
-        <v>-4.8788</v>
+        <v>-4.7454</v>
       </c>
       <c r="F20">
-        <v>2.4012</v>
+        <v>2.5346</v>
       </c>
       <c r="G20">
         <v>2.16</v>
@@ -3189,28 +3189,28 @@
         <v>2.12</v>
       </c>
       <c r="M20">
-        <v>0.12078036</v>
+        <v>0.12749038</v>
       </c>
       <c r="N20">
-        <v>1.99921964</v>
+        <v>1.99250962</v>
       </c>
       <c r="O20">
-        <v>0.3998439280000001</v>
+        <v>0.3985019240000001</v>
       </c>
       <c r="P20">
-        <v>1.599375712</v>
+        <v>1.594007696</v>
       </c>
       <c r="Q20">
-        <v>2.179375712</v>
+        <v>2.174007696</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1042037370630198</v>
+        <v>0.1048021053542243</v>
       </c>
       <c r="T20">
-        <v>0.9034872377507364</v>
+        <v>0.9127438049117501</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3227,7 +3227,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>17.55252261212005</v>
+        <v>16.62870563253478</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3235,22 +3235,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09253530533692172</v>
+        <v>0.09238034628216719</v>
       </c>
       <c r="C21">
-        <v>11.58065425833215</v>
+        <v>11.4748047655108</v>
       </c>
       <c r="D21">
-        <v>11.95525425833215</v>
+        <v>11.9828047655108</v>
       </c>
       <c r="E21">
-        <v>-4.7454</v>
+        <v>-4.612</v>
       </c>
       <c r="F21">
-        <v>2.5346</v>
+        <v>2.668</v>
       </c>
       <c r="G21">
         <v>2.16</v>
@@ -3271,28 +3271,28 @@
         <v>2.12</v>
       </c>
       <c r="M21">
-        <v>0.12749038</v>
+        <v>0.1342004</v>
       </c>
       <c r="N21">
-        <v>1.99250962</v>
+        <v>1.9857996</v>
       </c>
       <c r="O21">
-        <v>0.3985019240000001</v>
+        <v>0.39715992</v>
       </c>
       <c r="P21">
-        <v>1.594007696</v>
+        <v>1.58863968</v>
       </c>
       <c r="Q21">
-        <v>2.174007696</v>
+        <v>2.16863968</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1048021053542243</v>
+        <v>0.105415432852709</v>
       </c>
       <c r="T21">
-        <v>0.9127438049117501</v>
+        <v>0.922231786251789</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3309,7 +3309,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>16.62870563253478</v>
+        <v>15.79727035090804</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3317,22 +3317,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09238034628216719</v>
+        <v>0.09222538722741268</v>
       </c>
       <c r="C22">
-        <v>11.4748047655108</v>
+        <v>11.36908254453685</v>
       </c>
       <c r="D22">
-        <v>11.9828047655108</v>
+        <v>12.01048254453685</v>
       </c>
       <c r="E22">
-        <v>-4.612</v>
+        <v>-4.4786</v>
       </c>
       <c r="F22">
-        <v>2.668</v>
+        <v>2.8014</v>
       </c>
       <c r="G22">
         <v>2.16</v>
@@ -3353,28 +3353,28 @@
         <v>2.12</v>
       </c>
       <c r="M22">
-        <v>0.1342004</v>
+        <v>0.14091042</v>
       </c>
       <c r="N22">
-        <v>1.9857996</v>
+        <v>1.97908958</v>
       </c>
       <c r="O22">
-        <v>0.39715992</v>
+        <v>0.395817916</v>
       </c>
       <c r="P22">
-        <v>1.58863968</v>
+        <v>1.583271664</v>
       </c>
       <c r="Q22">
-        <v>2.16863968</v>
+        <v>2.163271664</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.105415432852709</v>
+        <v>0.1060442876296363</v>
       </c>
       <c r="T22">
-        <v>0.922231786251789</v>
+        <v>0.9319599696510695</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3391,7 +3391,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>15.79727035090804</v>
+        <v>15.04501938181719</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3399,22 +3399,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09222538722741268</v>
+        <v>0.09207042817265818</v>
       </c>
       <c r="C23">
-        <v>11.36908254453685</v>
+        <v>11.26348847936628</v>
       </c>
       <c r="D23">
-        <v>12.01048254453685</v>
+        <v>12.03828847936628</v>
       </c>
       <c r="E23">
-        <v>-4.4786</v>
+        <v>-4.3452</v>
       </c>
       <c r="F23">
-        <v>2.8014</v>
+        <v>2.9348</v>
       </c>
       <c r="G23">
         <v>2.16</v>
@@ -3435,28 +3435,28 @@
         <v>2.12</v>
       </c>
       <c r="M23">
-        <v>0.14091042</v>
+        <v>0.14762044</v>
       </c>
       <c r="N23">
-        <v>1.97908958</v>
+        <v>1.97237956</v>
       </c>
       <c r="O23">
-        <v>0.395817916</v>
+        <v>0.394475912</v>
       </c>
       <c r="P23">
-        <v>1.583271664</v>
+        <v>1.577903648</v>
       </c>
       <c r="Q23">
-        <v>2.163271664</v>
+        <v>2.157903648</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1060442876296363</v>
+        <v>0.1066892668880233</v>
       </c>
       <c r="T23">
-        <v>0.9319599696510695</v>
+        <v>0.9419375936503316</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>15.04501938181719</v>
+        <v>14.36115486446186</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3481,22 +3481,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09207042817265818</v>
+        <v>0.09191546911790366</v>
       </c>
       <c r="C24">
-        <v>11.26348847936628</v>
+        <v>11.15802346216003</v>
       </c>
       <c r="D24">
-        <v>12.03828847936628</v>
+        <v>12.06622346216003</v>
       </c>
       <c r="E24">
-        <v>-4.3452</v>
+        <v>-4.2118</v>
       </c>
       <c r="F24">
-        <v>2.9348</v>
+        <v>3.0682</v>
       </c>
       <c r="G24">
         <v>2.16</v>
@@ -3517,28 +3517,28 @@
         <v>2.12</v>
       </c>
       <c r="M24">
-        <v>0.14762044</v>
+        <v>0.15433046</v>
       </c>
       <c r="N24">
-        <v>1.97237956</v>
+        <v>1.96566954</v>
       </c>
       <c r="O24">
-        <v>0.394475912</v>
+        <v>0.393133908</v>
       </c>
       <c r="P24">
-        <v>1.577903648</v>
+        <v>1.572535632</v>
       </c>
       <c r="Q24">
-        <v>2.157903648</v>
+        <v>2.152535632</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1066892668880233</v>
+        <v>0.1073509988544203</v>
       </c>
       <c r="T24">
-        <v>0.9419375936503316</v>
+        <v>0.9521743767145096</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>14.36115486446186</v>
+        <v>13.73675682687656</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09191546911790366</v>
+        <v>0.09176051006314916</v>
       </c>
       <c r="C25">
-        <v>11.15802346216003</v>
+        <v>11.05268839337934</v>
       </c>
       <c r="D25">
-        <v>12.06622346216003</v>
+        <v>12.09428839337934</v>
       </c>
       <c r="E25">
-        <v>-4.2118</v>
+        <v>-4.0784</v>
       </c>
       <c r="F25">
-        <v>3.0682</v>
+        <v>3.2016</v>
       </c>
       <c r="G25">
         <v>2.16</v>
@@ -3599,28 +3599,28 @@
         <v>2.12</v>
       </c>
       <c r="M25">
-        <v>0.15433046</v>
+        <v>0.16104048</v>
       </c>
       <c r="N25">
-        <v>1.96566954</v>
+        <v>1.95895952</v>
       </c>
       <c r="O25">
-        <v>0.393133908</v>
+        <v>0.391791904</v>
       </c>
       <c r="P25">
-        <v>1.572535632</v>
+        <v>1.567167616</v>
       </c>
       <c r="Q25">
-        <v>2.152535632</v>
+        <v>2.147167616</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1073509988544203</v>
+        <v>0.1080301448199331</v>
       </c>
       <c r="T25">
-        <v>0.9521743767145096</v>
+        <v>0.9626805488066922</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>13.73675682687656</v>
+        <v>13.16439195909004</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3645,22 +3645,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09176051006314913</v>
+        <v>0.09190555100839462</v>
       </c>
       <c r="C26">
-        <v>11.05268839337935</v>
+        <v>10.89301584787637</v>
       </c>
       <c r="D26">
-        <v>12.09428839337935</v>
+        <v>12.06801584787637</v>
       </c>
       <c r="E26">
-        <v>-4.0784</v>
+        <v>-3.945</v>
       </c>
       <c r="F26">
-        <v>3.2016</v>
+        <v>3.335</v>
       </c>
       <c r="G26">
         <v>2.16</v>
@@ -3681,45 +3681,45 @@
         <v>2.12</v>
       </c>
       <c r="M26">
-        <v>0.16104048</v>
+        <v>0.172753</v>
       </c>
       <c r="N26">
-        <v>1.95895952</v>
+        <v>1.947247</v>
       </c>
       <c r="O26">
-        <v>0.391791904</v>
+        <v>0.3894494000000001</v>
       </c>
       <c r="P26">
-        <v>1.567167616</v>
+        <v>1.5577976</v>
       </c>
       <c r="Q26">
-        <v>2.147167616</v>
+        <v>2.1377976</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1080301448199331</v>
+        <v>0.1087274013445262</v>
       </c>
       <c r="T26">
-        <v>0.962680548806692</v>
+        <v>0.9734668854879995</v>
       </c>
       <c r="U26">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V26">
         <v>0.2</v>
       </c>
       <c r="W26">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y26">
-        <v>13.16439195909004</v>
+        <v>12.27185634981737</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3727,22 +3727,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09190555100839462</v>
+        <v>0.09176259195364012</v>
       </c>
       <c r="C27">
-        <v>10.89301584787637</v>
+        <v>10.78551047301856</v>
       </c>
       <c r="D27">
-        <v>12.06801584787637</v>
+        <v>12.09391047301856</v>
       </c>
       <c r="E27">
-        <v>-3.945</v>
+        <v>-3.8116</v>
       </c>
       <c r="F27">
-        <v>3.335</v>
+        <v>3.4684</v>
       </c>
       <c r="G27">
         <v>2.16</v>
@@ -3763,28 +3763,28 @@
         <v>2.12</v>
       </c>
       <c r="M27">
-        <v>0.172753</v>
+        <v>0.17966312</v>
       </c>
       <c r="N27">
-        <v>1.947247</v>
+        <v>1.94033688</v>
       </c>
       <c r="O27">
-        <v>0.3894494000000001</v>
+        <v>0.388067376</v>
       </c>
       <c r="P27">
-        <v>1.5577976</v>
+        <v>1.552269504</v>
       </c>
       <c r="Q27">
-        <v>2.1377976</v>
+        <v>2.132269504</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1087274013445262</v>
+        <v>0.1094435026400542</v>
       </c>
       <c r="T27">
-        <v>0.9734668854879995</v>
+        <v>0.9845447447823154</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3801,7 +3801,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>12.27185634981737</v>
+        <v>11.79986187482439</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3809,22 +3809,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09176259195364012</v>
+        <v>0.09161963289888558</v>
       </c>
       <c r="C28">
-        <v>10.78551047301856</v>
+        <v>10.67811646252901</v>
       </c>
       <c r="D28">
-        <v>12.09391047301856</v>
+        <v>12.11991646252901</v>
       </c>
       <c r="E28">
-        <v>-3.8116</v>
+        <v>-3.6782</v>
       </c>
       <c r="F28">
-        <v>3.4684</v>
+        <v>3.6018</v>
       </c>
       <c r="G28">
         <v>2.16</v>
@@ -3845,28 +3845,28 @@
         <v>2.12</v>
       </c>
       <c r="M28">
-        <v>0.17966312</v>
+        <v>0.18657324</v>
       </c>
       <c r="N28">
-        <v>1.94033688</v>
+        <v>1.93342676</v>
       </c>
       <c r="O28">
-        <v>0.388067376</v>
+        <v>0.386685352</v>
       </c>
       <c r="P28">
-        <v>1.552269504</v>
+        <v>1.546741408</v>
       </c>
       <c r="Q28">
-        <v>2.132269504</v>
+        <v>2.126741408</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1094435026400542</v>
+        <v>0.1101792231491583</v>
       </c>
       <c r="T28">
-        <v>0.9845447447823154</v>
+        <v>0.995926107070996</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3883,7 +3883,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>11.79986187482439</v>
+        <v>11.3628299535346</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3891,22 +3891,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09161963289888558</v>
+        <v>0.09147667384413108</v>
       </c>
       <c r="C29">
-        <v>10.67811646252901</v>
+        <v>10.57083453636882</v>
       </c>
       <c r="D29">
-        <v>12.11991646252901</v>
+        <v>12.14603453636883</v>
       </c>
       <c r="E29">
-        <v>-3.6782</v>
+        <v>-3.5448</v>
       </c>
       <c r="F29">
-        <v>3.6018</v>
+        <v>3.7352</v>
       </c>
       <c r="G29">
         <v>2.16</v>
@@ -3927,28 +3927,28 @@
         <v>2.12</v>
       </c>
       <c r="M29">
-        <v>0.18657324</v>
+        <v>0.19348336</v>
       </c>
       <c r="N29">
-        <v>1.93342676</v>
+        <v>1.92651664</v>
       </c>
       <c r="O29">
-        <v>0.386685352</v>
+        <v>0.385303328</v>
       </c>
       <c r="P29">
-        <v>1.546741408</v>
+        <v>1.541213312</v>
       </c>
       <c r="Q29">
-        <v>2.126741408</v>
+        <v>2.121213312</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1101792231491583</v>
+        <v>0.1109353803390709</v>
       </c>
       <c r="T29">
-        <v>0.995926107070996</v>
+        <v>1.00762361831214</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>11.3628299535346</v>
+        <v>10.95701459805122</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3973,22 +3973,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09147667384413108</v>
+        <v>0.09133371478937657</v>
       </c>
       <c r="C30">
-        <v>10.57083453636882</v>
+        <v>10.46366542071848</v>
       </c>
       <c r="D30">
-        <v>12.14603453636883</v>
+        <v>12.17226542071848</v>
       </c>
       <c r="E30">
-        <v>-3.5448</v>
+        <v>-3.4114</v>
       </c>
       <c r="F30">
-        <v>3.7352</v>
+        <v>3.8686</v>
       </c>
       <c r="G30">
         <v>2.16</v>
@@ -4009,28 +4009,28 @@
         <v>2.12</v>
       </c>
       <c r="M30">
-        <v>0.19348336</v>
+        <v>0.20039348</v>
       </c>
       <c r="N30">
-        <v>1.92651664</v>
+        <v>1.91960652</v>
       </c>
       <c r="O30">
-        <v>0.385303328</v>
+        <v>0.383921304</v>
       </c>
       <c r="P30">
-        <v>1.541213312</v>
+        <v>1.535685216</v>
       </c>
       <c r="Q30">
-        <v>2.121213312</v>
+        <v>2.115685216</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1109353803390709</v>
+        <v>0.1117128377315163</v>
       </c>
       <c r="T30">
-        <v>1.00762361831214</v>
+        <v>1.019650636912189</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -4047,7 +4047,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>10.95701459805122</v>
+        <v>10.57918650846325</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4055,22 +4055,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09133371478937657</v>
+        <v>0.09119075573462203</v>
       </c>
       <c r="C31">
-        <v>10.46366542071848</v>
+        <v>10.35660984804517</v>
       </c>
       <c r="D31">
-        <v>12.17226542071848</v>
+        <v>12.19860984804517</v>
       </c>
       <c r="E31">
-        <v>-3.4114</v>
+        <v>-3.278</v>
       </c>
       <c r="F31">
-        <v>3.8686</v>
+        <v>4.002</v>
       </c>
       <c r="G31">
         <v>2.16</v>
@@ -4091,28 +4091,28 @@
         <v>2.12</v>
       </c>
       <c r="M31">
-        <v>0.20039348</v>
+        <v>0.2073036</v>
       </c>
       <c r="N31">
-        <v>1.91960652</v>
+        <v>1.9126964</v>
       </c>
       <c r="O31">
-        <v>0.383921304</v>
+        <v>0.38253928</v>
       </c>
       <c r="P31">
-        <v>1.535685216</v>
+        <v>1.53015712</v>
       </c>
       <c r="Q31">
-        <v>2.115685216</v>
+        <v>2.11015712</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1117128377315163</v>
+        <v>0.1125125081923172</v>
       </c>
       <c r="T31">
-        <v>1.019650636912189</v>
+        <v>1.032021284615097</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -4129,7 +4129,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>10.57918650846325</v>
+        <v>10.22654695818114</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4137,22 +4137,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09119075573462203</v>
+        <v>0.09104779667986754</v>
       </c>
       <c r="C32">
-        <v>10.35660984804517</v>
+        <v>10.2496685571709</v>
       </c>
       <c r="D32">
-        <v>12.19860984804517</v>
+        <v>12.2250685571709</v>
       </c>
       <c r="E32">
-        <v>-3.278</v>
+        <v>-3.144600000000001</v>
       </c>
       <c r="F32">
-        <v>4.002</v>
+        <v>4.1354</v>
       </c>
       <c r="G32">
         <v>2.16</v>
@@ -4173,28 +4173,28 @@
         <v>2.12</v>
       </c>
       <c r="M32">
-        <v>0.2073036</v>
+        <v>0.21421372</v>
       </c>
       <c r="N32">
-        <v>1.9126964</v>
+        <v>1.90578628</v>
       </c>
       <c r="O32">
-        <v>0.38253928</v>
+        <v>0.3811572560000001</v>
       </c>
       <c r="P32">
-        <v>1.53015712</v>
+        <v>1.524629024</v>
       </c>
       <c r="Q32">
-        <v>2.11015712</v>
+        <v>2.104629024</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1125125081923172</v>
+        <v>0.1133353575070544</v>
       </c>
       <c r="T32">
-        <v>1.032021284615097</v>
+        <v>1.04475050181664</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -4211,7 +4211,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>10.22654695818114</v>
+        <v>9.896658346626912</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4219,22 +4219,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09104779667986754</v>
+        <v>0.09134003762511302</v>
       </c>
       <c r="C33">
-        <v>10.2496685571709</v>
+        <v>10.06230287889575</v>
       </c>
       <c r="D33">
-        <v>12.2250685571709</v>
+        <v>12.17110287889575</v>
       </c>
       <c r="E33">
-        <v>-3.144600000000001</v>
+        <v>-3.011200000000001</v>
       </c>
       <c r="F33">
-        <v>4.1354</v>
+        <v>4.2688</v>
       </c>
       <c r="G33">
         <v>2.16</v>
@@ -4255,45 +4255,45 @@
         <v>2.12</v>
       </c>
       <c r="M33">
-        <v>0.21421372</v>
+        <v>0.2283808</v>
       </c>
       <c r="N33">
-        <v>1.90578628</v>
+        <v>1.8916192</v>
       </c>
       <c r="O33">
-        <v>0.3811572560000001</v>
+        <v>0.37832384</v>
       </c>
       <c r="P33">
-        <v>1.524629024</v>
+        <v>1.51329536</v>
       </c>
       <c r="Q33">
-        <v>2.104629024</v>
+        <v>2.09329536</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1133353575070544</v>
+        <v>0.114182408272225</v>
       </c>
       <c r="T33">
-        <v>1.04475050181664</v>
+        <v>1.057854107759405</v>
       </c>
       <c r="U33">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V33">
         <v>0.2</v>
       </c>
       <c r="W33">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>9.896658346626912</v>
+        <v>9.282741806666762</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4301,22 +4301,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09134003762511302</v>
+        <v>0.0912106785703585</v>
       </c>
       <c r="C34">
-        <v>10.06230287889575</v>
+        <v>9.952731640718987</v>
       </c>
       <c r="D34">
-        <v>12.17110287889575</v>
+        <v>12.19493164071899</v>
       </c>
       <c r="E34">
-        <v>-3.011200000000001</v>
+        <v>-2.8778</v>
       </c>
       <c r="F34">
-        <v>4.2688</v>
+        <v>4.402200000000001</v>
       </c>
       <c r="G34">
         <v>2.16</v>
@@ -4337,28 +4337,28 @@
         <v>2.12</v>
       </c>
       <c r="M34">
-        <v>0.2283808</v>
+        <v>0.2355177</v>
       </c>
       <c r="N34">
-        <v>1.8916192</v>
+        <v>1.8844823</v>
       </c>
       <c r="O34">
-        <v>0.37832384</v>
+        <v>0.37689646</v>
       </c>
       <c r="P34">
-        <v>1.51329536</v>
+        <v>1.50758584</v>
       </c>
       <c r="Q34">
-        <v>2.09329536</v>
+        <v>2.08758584</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.114182408272225</v>
+        <v>0.1150547441348634</v>
       </c>
       <c r="T34">
-        <v>1.057854107759405</v>
+        <v>1.071348866118372</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4375,7 +4375,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>9.282741806666762</v>
+        <v>9.001446600404131</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4383,22 +4383,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.0912106785703585</v>
+        <v>0.091081319515604</v>
       </c>
       <c r="C35">
-        <v>9.952731640718987</v>
+        <v>9.843253890164972</v>
       </c>
       <c r="D35">
-        <v>12.19493164071899</v>
+        <v>12.21885389016497</v>
       </c>
       <c r="E35">
-        <v>-2.8778</v>
+        <v>-2.7444</v>
       </c>
       <c r="F35">
-        <v>4.402200000000001</v>
+        <v>4.535600000000001</v>
       </c>
       <c r="G35">
         <v>2.16</v>
@@ -4419,28 +4419,28 @@
         <v>2.12</v>
       </c>
       <c r="M35">
-        <v>0.2355177</v>
+        <v>0.2426546</v>
       </c>
       <c r="N35">
-        <v>1.8844823</v>
+        <v>1.8773454</v>
       </c>
       <c r="O35">
-        <v>0.37689646</v>
+        <v>0.37546908</v>
       </c>
       <c r="P35">
-        <v>1.50758584</v>
+        <v>1.50187632</v>
       </c>
       <c r="Q35">
-        <v>2.08758584</v>
+        <v>2.08187632</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1150547441348634</v>
+        <v>0.1159535144175818</v>
       </c>
       <c r="T35">
-        <v>1.071348866118372</v>
+        <v>1.085252556548822</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4457,7 +4457,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>9.001446600404131</v>
+        <v>8.736698170980478</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4465,22 +4465,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.091081319515604</v>
+        <v>0.09095196046084947</v>
       </c>
       <c r="C36">
-        <v>9.843253890164972</v>
+        <v>9.733870178486482</v>
       </c>
       <c r="D36">
-        <v>12.21885389016497</v>
+        <v>12.24287017848648</v>
       </c>
       <c r="E36">
-        <v>-2.7444</v>
+        <v>-2.611</v>
       </c>
       <c r="F36">
-        <v>4.535600000000001</v>
+        <v>4.669</v>
       </c>
       <c r="G36">
         <v>2.16</v>
@@ -4501,28 +4501,28 @@
         <v>2.12</v>
       </c>
       <c r="M36">
-        <v>0.2426546</v>
+        <v>0.2497915</v>
       </c>
       <c r="N36">
-        <v>1.8773454</v>
+        <v>1.8702085</v>
       </c>
       <c r="O36">
-        <v>0.37546908</v>
+        <v>0.3740417</v>
       </c>
       <c r="P36">
-        <v>1.50187632</v>
+        <v>1.4961668</v>
       </c>
       <c r="Q36">
-        <v>2.08187632</v>
+        <v>2.0761668</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1159535144175818</v>
+        <v>0.1168799391705377</v>
       </c>
       <c r="T36">
-        <v>1.085252556548822</v>
+        <v>1.099584052838672</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4539,7 +4539,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>8.736698170980478</v>
+        <v>8.48707822323818</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4547,22 +4547,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09095196046084947</v>
+        <v>0.09082260140609495</v>
       </c>
       <c r="C37">
-        <v>9.733870178486482</v>
+        <v>9.624581061278793</v>
       </c>
       <c r="D37">
-        <v>12.24287017848648</v>
+        <v>12.26698106127879</v>
       </c>
       <c r="E37">
-        <v>-2.611</v>
+        <v>-2.4776</v>
       </c>
       <c r="F37">
-        <v>4.669</v>
+        <v>4.8024</v>
       </c>
       <c r="G37">
         <v>2.16</v>
@@ -4583,28 +4583,28 @@
         <v>2.12</v>
       </c>
       <c r="M37">
-        <v>0.2497915</v>
+        <v>0.2569284</v>
       </c>
       <c r="N37">
-        <v>1.8702085</v>
+        <v>1.8630716</v>
       </c>
       <c r="O37">
-        <v>0.3740417</v>
+        <v>0.3726143200000001</v>
       </c>
       <c r="P37">
-        <v>1.4961668</v>
+        <v>1.49045728</v>
       </c>
       <c r="Q37">
-        <v>2.0761668</v>
+        <v>2.07045728</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1168799391705377</v>
+        <v>0.1178353146970234</v>
       </c>
       <c r="T37">
-        <v>1.099584052838672</v>
+        <v>1.114363408387579</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4621,7 +4621,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>8.48707822323818</v>
+        <v>8.251326050370453</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09082260140609497</v>
+        <v>0.09069324235134044</v>
       </c>
       <c r="C38">
-        <v>9.624581061278793</v>
+        <v>9.515387098522542</v>
       </c>
       <c r="D38">
-        <v>12.26698106127879</v>
+        <v>12.29118709852254</v>
       </c>
       <c r="E38">
-        <v>-2.477600000000001</v>
+        <v>-2.344200000000001</v>
       </c>
       <c r="F38">
-        <v>4.8024</v>
+        <v>4.9358</v>
       </c>
       <c r="G38">
         <v>2.16</v>
@@ -4665,28 +4665,28 @@
         <v>2.12</v>
       </c>
       <c r="M38">
-        <v>0.2569283999999999</v>
+        <v>0.2640652999999999</v>
       </c>
       <c r="N38">
-        <v>1.8630716</v>
+        <v>1.8559347</v>
       </c>
       <c r="O38">
-        <v>0.3726143200000001</v>
+        <v>0.3711869400000001</v>
       </c>
       <c r="P38">
-        <v>1.49045728</v>
+        <v>1.48474776</v>
       </c>
       <c r="Q38">
-        <v>2.07045728</v>
+        <v>2.06474776</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1178353146970234</v>
+        <v>0.1188210196053023</v>
       </c>
       <c r="T38">
-        <v>1.114363408387578</v>
+        <v>1.129611949826927</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4703,7 +4703,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>8.251326050370455</v>
+        <v>8.02831723819828</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4711,22 +4711,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09069324235134044</v>
+        <v>0.09056388329658592</v>
       </c>
       <c r="C39">
-        <v>9.515387098522542</v>
+        <v>9.406288854627073</v>
       </c>
       <c r="D39">
-        <v>12.29118709852254</v>
+        <v>12.31548885462707</v>
       </c>
       <c r="E39">
-        <v>-2.344200000000001</v>
+        <v>-2.2108</v>
       </c>
       <c r="F39">
-        <v>4.9358</v>
+        <v>5.0692</v>
       </c>
       <c r="G39">
         <v>2.16</v>
@@ -4747,28 +4747,28 @@
         <v>2.12</v>
       </c>
       <c r="M39">
-        <v>0.2640652999999999</v>
+        <v>0.2712022</v>
       </c>
       <c r="N39">
-        <v>1.8559347</v>
+        <v>1.8487978</v>
       </c>
       <c r="O39">
-        <v>0.3711869400000001</v>
+        <v>0.36975956</v>
       </c>
       <c r="P39">
-        <v>1.48474776</v>
+        <v>1.47903824</v>
       </c>
       <c r="Q39">
-        <v>2.06474776</v>
+        <v>2.05903824</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1188210196053023</v>
+        <v>0.1198385214461063</v>
       </c>
       <c r="T39">
-        <v>1.129611949826927</v>
+        <v>1.145352379699802</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4785,7 +4785,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>8.02831723819828</v>
+        <v>7.817045731929904</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4793,22 +4793,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09056388329658592</v>
+        <v>0.0904345242418314</v>
       </c>
       <c r="C40">
-        <v>9.406288854627073</v>
+        <v>9.297286898474301</v>
       </c>
       <c r="D40">
-        <v>12.31548885462707</v>
+        <v>12.3398868984743</v>
       </c>
       <c r="E40">
-        <v>-2.2108</v>
+        <v>-2.0774</v>
       </c>
       <c r="F40">
-        <v>5.0692</v>
+        <v>5.2026</v>
       </c>
       <c r="G40">
         <v>2.16</v>
@@ -4829,28 +4829,28 @@
         <v>2.12</v>
       </c>
       <c r="M40">
-        <v>0.2712022</v>
+        <v>0.2783391</v>
       </c>
       <c r="N40">
-        <v>1.8487978</v>
+        <v>1.8416609</v>
       </c>
       <c r="O40">
-        <v>0.36975956</v>
+        <v>0.3683321800000001</v>
       </c>
       <c r="P40">
-        <v>1.47903824</v>
+        <v>1.47332872</v>
       </c>
       <c r="Q40">
-        <v>2.05903824</v>
+        <v>2.05332872</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1198385214461063</v>
+        <v>0.1208893840030023</v>
       </c>
       <c r="T40">
-        <v>1.145352379699802</v>
+        <v>1.161608889240642</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4867,7 +4867,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>7.817045731929904</v>
+        <v>7.616608661880419</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4875,22 +4875,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.0904345242418314</v>
+        <v>0.09056116518707689</v>
       </c>
       <c r="C41">
-        <v>9.297286898474301</v>
+        <v>9.140000517191542</v>
       </c>
       <c r="D41">
-        <v>12.3398868984743</v>
+        <v>12.31600051719154</v>
       </c>
       <c r="E41">
-        <v>-2.0774</v>
+        <v>-1.944</v>
       </c>
       <c r="F41">
-        <v>5.2026</v>
+        <v>5.336</v>
       </c>
       <c r="G41">
         <v>2.16</v>
@@ -4911,45 +4911,45 @@
         <v>2.12</v>
       </c>
       <c r="M41">
-        <v>0.2783391</v>
+        <v>0.2897448</v>
       </c>
       <c r="N41">
-        <v>1.8416609</v>
+        <v>1.8302552</v>
       </c>
       <c r="O41">
-        <v>0.3683321800000001</v>
+        <v>0.36605104</v>
       </c>
       <c r="P41">
-        <v>1.47332872</v>
+        <v>1.46420416</v>
       </c>
       <c r="Q41">
-        <v>2.05332872</v>
+        <v>2.04420416</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1208893840030023</v>
+        <v>0.1219752753117948</v>
       </c>
       <c r="T41">
-        <v>1.161608889240642</v>
+        <v>1.178407282432842</v>
       </c>
       <c r="U41">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V41">
         <v>0.2</v>
       </c>
       <c r="W41">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y41">
-        <v>7.616608661880419</v>
+        <v>7.316783597151701</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4957,22 +4957,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09056116518707689</v>
+        <v>0.09043820613232238</v>
       </c>
       <c r="C42">
-        <v>9.140000517191542</v>
+        <v>9.029791131072608</v>
       </c>
       <c r="D42">
-        <v>12.31600051719154</v>
+        <v>12.33919113107261</v>
       </c>
       <c r="E42">
-        <v>-1.944</v>
+        <v>-1.8106</v>
       </c>
       <c r="F42">
-        <v>5.336</v>
+        <v>5.4694</v>
       </c>
       <c r="G42">
         <v>2.16</v>
@@ -4993,28 +4993,28 @@
         <v>2.12</v>
       </c>
       <c r="M42">
-        <v>0.2897448</v>
+        <v>0.29698842</v>
       </c>
       <c r="N42">
-        <v>1.8302552</v>
+        <v>1.82301158</v>
       </c>
       <c r="O42">
-        <v>0.36605104</v>
+        <v>0.364602316</v>
       </c>
       <c r="P42">
-        <v>1.46420416</v>
+        <v>1.458409264</v>
       </c>
       <c r="Q42">
-        <v>2.04420416</v>
+        <v>2.038409264</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1219752753117948</v>
+        <v>0.1230979764954617</v>
       </c>
       <c r="T42">
-        <v>1.178407282432842</v>
+        <v>1.195775112682405</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -5031,7 +5031,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>7.316783597151701</v>
+        <v>7.138325460635805</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5039,22 +5039,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09043820613232238</v>
+        <v>0.09031524707756788</v>
       </c>
       <c r="C43">
-        <v>9.029791131072608</v>
+        <v>8.91966924400009</v>
       </c>
       <c r="D43">
-        <v>12.33919113107261</v>
+        <v>12.36246924400009</v>
       </c>
       <c r="E43">
-        <v>-1.8106</v>
+        <v>-1.6772</v>
       </c>
       <c r="F43">
-        <v>5.4694</v>
+        <v>5.6028</v>
       </c>
       <c r="G43">
         <v>2.16</v>
@@ -5075,28 +5075,28 @@
         <v>2.12</v>
       </c>
       <c r="M43">
-        <v>0.29698842</v>
+        <v>0.30423204</v>
       </c>
       <c r="N43">
-        <v>1.82301158</v>
+        <v>1.81576796</v>
       </c>
       <c r="O43">
-        <v>0.364602316</v>
+        <v>0.363153592</v>
       </c>
       <c r="P43">
-        <v>1.458409264</v>
+        <v>1.452614368</v>
       </c>
       <c r="Q43">
-        <v>2.038409264</v>
+        <v>2.032614368</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1230979764954617</v>
+        <v>0.1242593915130481</v>
       </c>
       <c r="T43">
-        <v>1.195775112682405</v>
+        <v>1.213741833630228</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -5113,7 +5113,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>7.138325460635805</v>
+        <v>6.968365330620666</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5121,22 +5121,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09031524707756788</v>
+        <v>0.09019228802281337</v>
       </c>
       <c r="C44">
-        <v>8.91966924400009</v>
+        <v>8.809635352115698</v>
       </c>
       <c r="D44">
-        <v>12.36246924400009</v>
+        <v>12.3858353521157</v>
       </c>
       <c r="E44">
-        <v>-1.677200000000001</v>
+        <v>-1.5438</v>
       </c>
       <c r="F44">
-        <v>5.602799999999999</v>
+        <v>5.7362</v>
       </c>
       <c r="G44">
         <v>2.16</v>
@@ -5157,28 +5157,28 @@
         <v>2.12</v>
       </c>
       <c r="M44">
-        <v>0.30423204</v>
+        <v>0.31147566</v>
       </c>
       <c r="N44">
-        <v>1.81576796</v>
+        <v>1.80852434</v>
       </c>
       <c r="O44">
-        <v>0.363153592</v>
+        <v>0.361704868</v>
       </c>
       <c r="P44">
-        <v>1.452614368</v>
+        <v>1.446819472</v>
       </c>
       <c r="Q44">
-        <v>2.032614368</v>
+        <v>2.026819472</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.124259391513048</v>
+        <v>0.1254615579347603</v>
       </c>
       <c r="T44">
-        <v>1.213741833630228</v>
+        <v>1.232338965839379</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -5195,7 +5195,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>6.968365330620667</v>
+        <v>6.806310322931814</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5203,22 +5203,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09019228802281337</v>
+        <v>0.09006932896805886</v>
       </c>
       <c r="C45">
-        <v>8.809635352115698</v>
+        <v>8.699689955319233</v>
       </c>
       <c r="D45">
-        <v>12.3858353521157</v>
+        <v>12.40928995531923</v>
       </c>
       <c r="E45">
-        <v>-1.5438</v>
+        <v>-1.4104</v>
       </c>
       <c r="F45">
-        <v>5.7362</v>
+        <v>5.8696</v>
       </c>
       <c r="G45">
         <v>2.16</v>
@@ -5239,28 +5239,28 @@
         <v>2.12</v>
       </c>
       <c r="M45">
-        <v>0.31147566</v>
+        <v>0.31871928</v>
       </c>
       <c r="N45">
-        <v>1.80852434</v>
+        <v>1.80128072</v>
       </c>
       <c r="O45">
-        <v>0.361704868</v>
+        <v>0.3602561440000001</v>
       </c>
       <c r="P45">
-        <v>1.446819472</v>
+        <v>1.441024576</v>
       </c>
       <c r="Q45">
-        <v>2.026819472</v>
+        <v>2.021024576</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1254615579347603</v>
+        <v>0.1267066588715337</v>
       </c>
       <c r="T45">
-        <v>1.232338965839379</v>
+        <v>1.251600281341714</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5277,7 +5277,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>6.806310322931814</v>
+        <v>6.651621451956092</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5285,22 +5285,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09006932896805886</v>
+        <v>0.08994636991330432</v>
       </c>
       <c r="C46">
-        <v>8.699689955319233</v>
+        <v>8.589833557304255</v>
       </c>
       <c r="D46">
-        <v>12.40928995531923</v>
+        <v>12.43283355730425</v>
       </c>
       <c r="E46">
-        <v>-1.4104</v>
+        <v>-1.277</v>
       </c>
       <c r="F46">
-        <v>5.8696</v>
+        <v>6.003</v>
       </c>
       <c r="G46">
         <v>2.16</v>
@@ -5321,28 +5321,28 @@
         <v>2.12</v>
       </c>
       <c r="M46">
-        <v>0.31871928</v>
+        <v>0.3259629</v>
       </c>
       <c r="N46">
-        <v>1.80128072</v>
+        <v>1.7940371</v>
       </c>
       <c r="O46">
-        <v>0.3602561440000001</v>
+        <v>0.35880742</v>
       </c>
       <c r="P46">
-        <v>1.441024576</v>
+        <v>1.43522968</v>
       </c>
       <c r="Q46">
-        <v>2.021024576</v>
+        <v>2.01522968</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1267066588715337</v>
+        <v>0.1279970362060079</v>
       </c>
       <c r="T46">
-        <v>1.251600281341714</v>
+        <v>1.271562008316861</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5359,7 +5359,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>6.651621451956092</v>
+        <v>6.503807641912623</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5367,22 +5367,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08994636991330432</v>
+        <v>0.08982341085854981</v>
       </c>
       <c r="C47">
-        <v>8.589833557304255</v>
+        <v>8.480066665594116</v>
       </c>
       <c r="D47">
-        <v>12.43283355730425</v>
+        <v>12.45646666559412</v>
       </c>
       <c r="E47">
-        <v>-1.277</v>
+        <v>-1.1436</v>
       </c>
       <c r="F47">
-        <v>6.003</v>
+        <v>6.1364</v>
       </c>
       <c r="G47">
         <v>2.16</v>
@@ -5403,28 +5403,28 @@
         <v>2.12</v>
       </c>
       <c r="M47">
-        <v>0.3259629</v>
+        <v>0.33320652</v>
       </c>
       <c r="N47">
-        <v>1.7940371</v>
+        <v>1.78679348</v>
       </c>
       <c r="O47">
-        <v>0.35880742</v>
+        <v>0.357358696</v>
       </c>
       <c r="P47">
-        <v>1.43522968</v>
+        <v>1.429434784</v>
       </c>
       <c r="Q47">
-        <v>2.01522968</v>
+        <v>2.009434784</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1279970362060079</v>
+        <v>0.1293352052936108</v>
       </c>
       <c r="T47">
-        <v>1.271562008316861</v>
+        <v>1.292263058513309</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5441,7 +5441,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>6.503807641912623</v>
+        <v>6.362420519262348</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5449,22 +5449,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08982341085854981</v>
+        <v>0.08970045180379529</v>
       </c>
       <c r="C48">
-        <v>8.480066665594116</v>
+        <v>8.37038979157847</v>
       </c>
       <c r="D48">
-        <v>12.45646666559412</v>
+        <v>12.48018979157847</v>
       </c>
       <c r="E48">
-        <v>-1.1436</v>
+        <v>-1.0102</v>
       </c>
       <c r="F48">
-        <v>6.1364</v>
+        <v>6.2698</v>
       </c>
       <c r="G48">
         <v>2.16</v>
@@ -5485,28 +5485,28 @@
         <v>2.12</v>
       </c>
       <c r="M48">
-        <v>0.33320652</v>
+        <v>0.34045014</v>
       </c>
       <c r="N48">
-        <v>1.78679348</v>
+        <v>1.77954986</v>
       </c>
       <c r="O48">
-        <v>0.357358696</v>
+        <v>0.3559099720000001</v>
       </c>
       <c r="P48">
-        <v>1.429434784</v>
+        <v>1.423639888</v>
       </c>
       <c r="Q48">
-        <v>2.009434784</v>
+        <v>2.003639888</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1293352052936108</v>
+        <v>0.1307238713279157</v>
       </c>
       <c r="T48">
-        <v>1.292263058513309</v>
+        <v>1.313745280415284</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5523,7 +5523,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>6.362420519262348</v>
+        <v>6.227049869916341</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5531,22 +5531,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08970045180379529</v>
+        <v>0.08996149274904078</v>
       </c>
       <c r="C49">
-        <v>8.37038979157847</v>
+        <v>8.186733093268556</v>
       </c>
       <c r="D49">
-        <v>12.48018979157847</v>
+        <v>12.42993309326856</v>
       </c>
       <c r="E49">
-        <v>-1.0102</v>
+        <v>-0.8768000000000002</v>
       </c>
       <c r="F49">
-        <v>6.2698</v>
+        <v>6.4032</v>
       </c>
       <c r="G49">
         <v>2.16</v>
@@ -5567,45 +5567,45 @@
         <v>2.12</v>
       </c>
       <c r="M49">
-        <v>0.34045014</v>
+        <v>0.35409696</v>
       </c>
       <c r="N49">
-        <v>1.77954986</v>
+        <v>1.76590304</v>
       </c>
       <c r="O49">
-        <v>0.3559099720000001</v>
+        <v>0.353180608</v>
       </c>
       <c r="P49">
-        <v>1.423639888</v>
+        <v>1.412722432</v>
       </c>
       <c r="Q49">
-        <v>2.003639888</v>
+        <v>1.992722432</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1307238713279157</v>
+        <v>0.1321659475943092</v>
       </c>
       <c r="T49">
-        <v>1.313745280415284</v>
+        <v>1.336053741621182</v>
       </c>
       <c r="U49">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V49">
         <v>0.2</v>
       </c>
       <c r="W49">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y49">
-        <v>6.227049869916341</v>
+        <v>5.987060719188326</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5613,22 +5613,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08996149274904078</v>
+        <v>0.08984653369428626</v>
       </c>
       <c r="C50">
-        <v>8.186733093268556</v>
+        <v>8.075415528639574</v>
       </c>
       <c r="D50">
-        <v>12.42993309326856</v>
+        <v>12.45201552863957</v>
       </c>
       <c r="E50">
-        <v>-0.8768000000000002</v>
+        <v>-0.7434000000000003</v>
       </c>
       <c r="F50">
-        <v>6.4032</v>
+        <v>6.5366</v>
       </c>
       <c r="G50">
         <v>2.16</v>
@@ -5649,28 +5649,28 @@
         <v>2.12</v>
       </c>
       <c r="M50">
-        <v>0.35409696</v>
+        <v>0.36147398</v>
       </c>
       <c r="N50">
-        <v>1.76590304</v>
+        <v>1.75852602</v>
       </c>
       <c r="O50">
-        <v>0.353180608</v>
+        <v>0.351705204</v>
       </c>
       <c r="P50">
-        <v>1.412722432</v>
+        <v>1.406820816</v>
       </c>
       <c r="Q50">
-        <v>1.992722432</v>
+        <v>1.986820816</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1321659475943092</v>
+        <v>0.1336645758711495</v>
       </c>
       <c r="T50">
-        <v>1.336053741621182</v>
+        <v>1.359237044442996</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5687,7 +5687,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.987060719188326</v>
+        <v>5.864875806551829</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08984653369428626</v>
+        <v>0.08973157463953174</v>
       </c>
       <c r="C51">
-        <v>8.075415528639574</v>
+        <v>7.964176564884404</v>
       </c>
       <c r="D51">
-        <v>12.45201552863957</v>
+        <v>12.4741765648844</v>
       </c>
       <c r="E51">
-        <v>-0.7434000000000003</v>
+        <v>-0.6100000000000003</v>
       </c>
       <c r="F51">
-        <v>6.5366</v>
+        <v>6.67</v>
       </c>
       <c r="G51">
         <v>2.16</v>
@@ -5731,28 +5731,28 @@
         <v>2.12</v>
       </c>
       <c r="M51">
-        <v>0.36147398</v>
+        <v>0.368851</v>
       </c>
       <c r="N51">
-        <v>1.75852602</v>
+        <v>1.751149</v>
       </c>
       <c r="O51">
-        <v>0.351705204</v>
+        <v>0.3502298</v>
       </c>
       <c r="P51">
-        <v>1.406820816</v>
+        <v>1.4009192</v>
       </c>
       <c r="Q51">
-        <v>1.986820816</v>
+        <v>1.9809192</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1336645758711495</v>
+        <v>0.1352231492790635</v>
       </c>
       <c r="T51">
-        <v>1.359237044442996</v>
+        <v>1.383347679377684</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5769,7 +5769,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.864875806551829</v>
+        <v>5.747578290420794</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5777,22 +5777,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08973157463953174</v>
+        <v>0.08961661558477724</v>
       </c>
       <c r="C52">
-        <v>7.964176564884404</v>
+        <v>7.853016622412666</v>
       </c>
       <c r="D52">
-        <v>12.4741765648844</v>
+        <v>12.49641662241267</v>
       </c>
       <c r="E52">
-        <v>-0.6100000000000003</v>
+        <v>-0.4766000000000004</v>
       </c>
       <c r="F52">
-        <v>6.67</v>
+        <v>6.8034</v>
       </c>
       <c r="G52">
         <v>2.16</v>
@@ -5813,28 +5813,28 @@
         <v>2.12</v>
       </c>
       <c r="M52">
-        <v>0.368851</v>
+        <v>0.37622802</v>
       </c>
       <c r="N52">
-        <v>1.751149</v>
+        <v>1.74377198</v>
       </c>
       <c r="O52">
-        <v>0.3502298</v>
+        <v>0.348754396</v>
       </c>
       <c r="P52">
-        <v>1.4009192</v>
+        <v>1.395017584</v>
       </c>
       <c r="Q52">
-        <v>1.9809192</v>
+        <v>1.975017584</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1352231492790635</v>
+        <v>0.1368453379281168</v>
       </c>
       <c r="T52">
-        <v>1.383347679377684</v>
+        <v>1.408442421860726</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5851,7 +5851,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.747578290420794</v>
+        <v>5.634880676883131</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5859,22 +5859,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08961661558477724</v>
+        <v>0.08950165653002272</v>
       </c>
       <c r="C53">
-        <v>7.853016622412666</v>
+        <v>7.741936124637514</v>
       </c>
       <c r="D53">
-        <v>12.49641662241267</v>
+        <v>12.51873612463751</v>
       </c>
       <c r="E53">
-        <v>-0.4766000000000004</v>
+        <v>-0.3432000000000004</v>
       </c>
       <c r="F53">
-        <v>6.8034</v>
+        <v>6.9368</v>
       </c>
       <c r="G53">
         <v>2.16</v>
@@ -5895,28 +5895,28 @@
         <v>2.12</v>
       </c>
       <c r="M53">
-        <v>0.37622802</v>
+        <v>0.38360504</v>
       </c>
       <c r="N53">
-        <v>1.74377198</v>
+        <v>1.73639496</v>
       </c>
       <c r="O53">
-        <v>0.348754396</v>
+        <v>0.3472789920000001</v>
       </c>
       <c r="P53">
-        <v>1.395017584</v>
+        <v>1.389115968</v>
       </c>
       <c r="Q53">
-        <v>1.975017584</v>
+        <v>1.969115968</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1368453379281168</v>
+        <v>0.1385351177708807</v>
       </c>
       <c r="T53">
-        <v>1.408442421860726</v>
+        <v>1.434582778613894</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5933,7 +5933,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.634880676883131</v>
+        <v>5.52651758694307</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5941,22 +5941,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08950165653002272</v>
+        <v>0.0893866974752682</v>
       </c>
       <c r="C54">
-        <v>7.741936124637514</v>
+        <v>7.630935498002494</v>
       </c>
       <c r="D54">
-        <v>12.51873612463751</v>
+        <v>12.54113549800249</v>
       </c>
       <c r="E54">
-        <v>-0.3432000000000004</v>
+        <v>-0.2097999999999995</v>
       </c>
       <c r="F54">
-        <v>6.9368</v>
+        <v>7.070200000000001</v>
       </c>
       <c r="G54">
         <v>2.16</v>
@@ -5977,28 +5977,28 @@
         <v>2.12</v>
       </c>
       <c r="M54">
-        <v>0.38360504</v>
+        <v>0.3909820600000001</v>
       </c>
       <c r="N54">
-        <v>1.73639496</v>
+        <v>1.72901794</v>
       </c>
       <c r="O54">
-        <v>0.3472789920000001</v>
+        <v>0.3458035880000001</v>
       </c>
       <c r="P54">
-        <v>1.389115968</v>
+        <v>1.383214352</v>
       </c>
       <c r="Q54">
-        <v>1.969115968</v>
+        <v>1.963214352</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1385351177708807</v>
+        <v>0.1402968031388685</v>
       </c>
       <c r="T54">
-        <v>1.434582778613894</v>
+        <v>1.461835490973581</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -6015,7 +6015,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.52651758694307</v>
+        <v>5.422243670208295</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6023,22 +6023,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.0893866974752682</v>
+        <v>0.0892717384205137</v>
       </c>
       <c r="C55">
-        <v>7.630935498002494</v>
+        <v>7.520015172008716</v>
       </c>
       <c r="D55">
-        <v>12.54113549800249</v>
+        <v>12.56361517200872</v>
       </c>
       <c r="E55">
-        <v>-0.2097999999999995</v>
+        <v>-0.07639999999999958</v>
       </c>
       <c r="F55">
-        <v>7.070200000000001</v>
+        <v>7.203600000000001</v>
       </c>
       <c r="G55">
         <v>2.16</v>
@@ -6059,28 +6059,28 @@
         <v>2.12</v>
       </c>
       <c r="M55">
-        <v>0.3909820600000001</v>
+        <v>0.39835908</v>
       </c>
       <c r="N55">
-        <v>1.72901794</v>
+        <v>1.72164092</v>
       </c>
       <c r="O55">
-        <v>0.3458035880000001</v>
+        <v>0.344328184</v>
       </c>
       <c r="P55">
-        <v>1.383214352</v>
+        <v>1.377312736</v>
       </c>
       <c r="Q55">
-        <v>1.963214352</v>
+        <v>1.957312736</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1402968031388685</v>
+        <v>0.1421350835228558</v>
       </c>
       <c r="T55">
-        <v>1.461835490973581</v>
+        <v>1.490273103870645</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -6097,7 +6097,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.422243670208295</v>
+        <v>5.321831750389623</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6105,22 +6105,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.0892717384205137</v>
+        <v>0.08915677936575918</v>
       </c>
       <c r="C56">
-        <v>7.520015172008716</v>
+        <v>7.409175579242297</v>
       </c>
       <c r="D56">
-        <v>12.56361517200872</v>
+        <v>12.5861755792423</v>
       </c>
       <c r="E56">
-        <v>-0.07639999999999958</v>
+        <v>0.05700000000000038</v>
       </c>
       <c r="F56">
-        <v>7.203600000000001</v>
+        <v>7.337000000000001</v>
       </c>
       <c r="G56">
         <v>2.16</v>
@@ -6141,28 +6141,28 @@
         <v>2.12</v>
       </c>
       <c r="M56">
-        <v>0.39835908</v>
+        <v>0.4057361</v>
       </c>
       <c r="N56">
-        <v>1.72164092</v>
+        <v>1.7142639</v>
       </c>
       <c r="O56">
-        <v>0.344328184</v>
+        <v>0.3428527800000001</v>
       </c>
       <c r="P56">
-        <v>1.377312736</v>
+        <v>1.37141112</v>
       </c>
       <c r="Q56">
-        <v>1.957312736</v>
+        <v>1.95141112</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1421350835228558</v>
+        <v>0.1440550652572426</v>
       </c>
       <c r="T56">
-        <v>1.490273103870645</v>
+        <v>1.519974610674245</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -6179,7 +6179,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.321831750389623</v>
+        <v>5.225071173109812</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6187,22 +6187,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08915677936575918</v>
+        <v>0.08904182031100466</v>
       </c>
       <c r="C57">
-        <v>7.409175579242297</v>
+        <v>7.29841715540211</v>
       </c>
       <c r="D57">
-        <v>12.5861755792423</v>
+        <v>12.60881715540211</v>
       </c>
       <c r="E57">
-        <v>0.05700000000000038</v>
+        <v>0.1904000000000003</v>
       </c>
       <c r="F57">
-        <v>7.337000000000001</v>
+        <v>7.470400000000001</v>
       </c>
       <c r="G57">
         <v>2.16</v>
@@ -6223,28 +6223,28 @@
         <v>2.12</v>
       </c>
       <c r="M57">
-        <v>0.4057361</v>
+        <v>0.4131131200000001</v>
       </c>
       <c r="N57">
-        <v>1.7142639</v>
+        <v>1.70688688</v>
       </c>
       <c r="O57">
-        <v>0.3428527800000001</v>
+        <v>0.3413773760000001</v>
       </c>
       <c r="P57">
-        <v>1.37141112</v>
+        <v>1.365509504</v>
       </c>
       <c r="Q57">
-        <v>1.95141112</v>
+        <v>1.945509504</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1440550652572426</v>
+        <v>0.146062318888647</v>
       </c>
       <c r="T57">
-        <v>1.519974610674245</v>
+        <v>1.551026185968918</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.225071173109812</v>
+        <v>5.131766330732851</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6269,22 +6269,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08904182031100466</v>
+        <v>0.08892686125625016</v>
       </c>
       <c r="C58">
-        <v>7.29841715540211</v>
+        <v>7.187740339327838</v>
       </c>
       <c r="D58">
-        <v>12.60881715540211</v>
+        <v>12.63154033932784</v>
       </c>
       <c r="E58">
-        <v>0.1904000000000003</v>
+        <v>0.3238000000000003</v>
       </c>
       <c r="F58">
-        <v>7.470400000000001</v>
+        <v>7.603800000000001</v>
       </c>
       <c r="G58">
         <v>2.16</v>
@@ -6305,28 +6305,28 @@
         <v>2.12</v>
       </c>
       <c r="M58">
-        <v>0.4131131200000001</v>
+        <v>0.4204901400000001</v>
       </c>
       <c r="N58">
-        <v>1.70688688</v>
+        <v>1.69950986</v>
       </c>
       <c r="O58">
-        <v>0.3413773760000001</v>
+        <v>0.3399019720000001</v>
       </c>
       <c r="P58">
-        <v>1.365509504</v>
+        <v>1.359607888</v>
       </c>
       <c r="Q58">
-        <v>1.945509504</v>
+        <v>1.939607888</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.146062318888647</v>
+        <v>0.1481629331540701</v>
       </c>
       <c r="T58">
-        <v>1.551026185968918</v>
+        <v>1.583522020579623</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6343,7 +6343,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.131766330732851</v>
+        <v>5.04173534247438</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6351,22 +6351,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08892686125625016</v>
+        <v>0.08881190220149564</v>
       </c>
       <c r="C59">
-        <v>7.187740339327838</v>
+        <v>7.077145573028328</v>
       </c>
       <c r="D59">
-        <v>12.63154033932784</v>
+        <v>12.65434557302833</v>
       </c>
       <c r="E59">
-        <v>0.3238000000000003</v>
+        <v>0.4572000000000003</v>
       </c>
       <c r="F59">
-        <v>7.603800000000001</v>
+        <v>7.737200000000001</v>
       </c>
       <c r="G59">
         <v>2.16</v>
@@ -6387,28 +6387,28 @@
         <v>2.12</v>
       </c>
       <c r="M59">
-        <v>0.4204901400000001</v>
+        <v>0.42786716</v>
       </c>
       <c r="N59">
-        <v>1.69950986</v>
+        <v>1.69213284</v>
       </c>
       <c r="O59">
-        <v>0.3399019720000001</v>
+        <v>0.338426568</v>
       </c>
       <c r="P59">
-        <v>1.359607888</v>
+        <v>1.353706272</v>
       </c>
       <c r="Q59">
-        <v>1.939607888</v>
+        <v>1.933706272</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1481629331540701</v>
+        <v>0.1503635766702277</v>
       </c>
       <c r="T59">
-        <v>1.583522020579623</v>
+        <v>1.617565275886075</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.04173534247438</v>
+        <v>4.954808871052409</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6433,22 +6433,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08881190220149562</v>
+        <v>0.08869694314674112</v>
       </c>
       <c r="C60">
-        <v>7.07714557302833</v>
+        <v>6.966633301710237</v>
       </c>
       <c r="D60">
-        <v>12.65434557302833</v>
+        <v>12.67723330171024</v>
       </c>
       <c r="E60">
-        <v>0.4571999999999994</v>
+        <v>0.5905999999999993</v>
       </c>
       <c r="F60">
-        <v>7.7372</v>
+        <v>7.8706</v>
       </c>
       <c r="G60">
         <v>2.16</v>
@@ -6469,28 +6469,28 @@
         <v>2.12</v>
       </c>
       <c r="M60">
-        <v>0.42786716</v>
+        <v>0.43524418</v>
       </c>
       <c r="N60">
-        <v>1.69213284</v>
+        <v>1.68475582</v>
       </c>
       <c r="O60">
-        <v>0.338426568</v>
+        <v>0.336951164</v>
       </c>
       <c r="P60">
-        <v>1.353706272</v>
+        <v>1.347804656</v>
       </c>
       <c r="Q60">
-        <v>1.933706272</v>
+        <v>1.927804656</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1503635766702276</v>
+        <v>0.1526715686505881</v>
       </c>
       <c r="T60">
-        <v>1.617565275886074</v>
+        <v>1.653269177792841</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6507,7 +6507,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.954808871052409</v>
+        <v>4.870829059678639</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6515,22 +6515,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08869694314674112</v>
+        <v>0.0885819840919866</v>
       </c>
       <c r="C61">
-        <v>6.966633301710237</v>
+        <v>6.856203973807018</v>
       </c>
       <c r="D61">
-        <v>12.67723330171024</v>
+        <v>12.70020397380702</v>
       </c>
       <c r="E61">
-        <v>0.5905999999999993</v>
+        <v>0.7239999999999993</v>
       </c>
       <c r="F61">
-        <v>7.8706</v>
+        <v>8.004</v>
       </c>
       <c r="G61">
         <v>2.16</v>
@@ -6551,28 +6551,28 @@
         <v>2.12</v>
       </c>
       <c r="M61">
-        <v>0.43524418</v>
+        <v>0.4426212</v>
       </c>
       <c r="N61">
-        <v>1.68475582</v>
+        <v>1.6773788</v>
       </c>
       <c r="O61">
-        <v>0.336951164</v>
+        <v>0.33547576</v>
       </c>
       <c r="P61">
-        <v>1.347804656</v>
+        <v>1.34190304</v>
       </c>
       <c r="Q61">
-        <v>1.927804656</v>
+        <v>1.92190304</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1526715686505881</v>
+        <v>0.1550949602299665</v>
       </c>
       <c r="T61">
-        <v>1.653269177792841</v>
+        <v>1.690758274794947</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6589,7 +6589,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.870829059678639</v>
+        <v>4.789648575350661</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6597,22 +6597,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.0885819840919866</v>
+        <v>0.08846702503723208</v>
       </c>
       <c r="C62">
-        <v>6.856203973807018</v>
+        <v>6.745858041008205</v>
       </c>
       <c r="D62">
-        <v>12.70020397380702</v>
+        <v>12.7232580410082</v>
       </c>
       <c r="E62">
-        <v>0.7239999999999993</v>
+        <v>0.8573999999999993</v>
       </c>
       <c r="F62">
-        <v>8.004</v>
+        <v>8.1374</v>
       </c>
       <c r="G62">
         <v>2.16</v>
@@ -6633,28 +6633,28 @@
         <v>2.12</v>
       </c>
       <c r="M62">
-        <v>0.4426212</v>
+        <v>0.44999822</v>
       </c>
       <c r="N62">
-        <v>1.6773788</v>
+        <v>1.67000178</v>
       </c>
       <c r="O62">
-        <v>0.33547576</v>
+        <v>0.3340003560000001</v>
       </c>
       <c r="P62">
-        <v>1.34190304</v>
+        <v>1.336001424</v>
       </c>
       <c r="Q62">
-        <v>1.92190304</v>
+        <v>1.916001424</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1550949602299665</v>
+        <v>0.1576426283005951</v>
       </c>
       <c r="T62">
-        <v>1.690758274794947</v>
+        <v>1.730169889592032</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6671,7 +6671,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.789648575350661</v>
+        <v>4.711129746246552</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6679,22 +6679,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08846702503723208</v>
+        <v>0.08835206598247757</v>
       </c>
       <c r="C63">
-        <v>6.745858041008205</v>
+        <v>6.635595958289011</v>
       </c>
       <c r="D63">
-        <v>12.7232580410082</v>
+        <v>12.74639595828901</v>
       </c>
       <c r="E63">
-        <v>0.8573999999999993</v>
+        <v>0.9907999999999992</v>
       </c>
       <c r="F63">
-        <v>8.1374</v>
+        <v>8.270799999999999</v>
       </c>
       <c r="G63">
         <v>2.16</v>
@@ -6715,28 +6715,28 @@
         <v>2.12</v>
       </c>
       <c r="M63">
-        <v>0.44999822</v>
+        <v>0.45737524</v>
       </c>
       <c r="N63">
-        <v>1.67000178</v>
+        <v>1.66262476</v>
       </c>
       <c r="O63">
-        <v>0.3340003560000001</v>
+        <v>0.332524952</v>
       </c>
       <c r="P63">
-        <v>1.336001424</v>
+        <v>1.330099808</v>
       </c>
       <c r="Q63">
-        <v>1.916001424</v>
+        <v>1.910099808</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1576426283005951</v>
+        <v>0.1603243841644146</v>
       </c>
       <c r="T63">
-        <v>1.730169889592032</v>
+        <v>1.771655799904753</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6753,7 +6753,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.711129746246552</v>
+        <v>4.635143782597415</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08835206598247757</v>
+        <v>0.08823710692772306</v>
       </c>
       <c r="C64">
-        <v>6.635595958289011</v>
+        <v>6.525418183940269</v>
       </c>
       <c r="D64">
-        <v>12.74639595828901</v>
+        <v>12.76961818394027</v>
       </c>
       <c r="E64">
-        <v>0.9907999999999992</v>
+        <v>1.124199999999999</v>
       </c>
       <c r="F64">
-        <v>8.270799999999999</v>
+        <v>8.404199999999999</v>
       </c>
       <c r="G64">
         <v>2.16</v>
@@ -6797,28 +6797,28 @@
         <v>2.12</v>
       </c>
       <c r="M64">
-        <v>0.45737524</v>
+        <v>0.46475226</v>
       </c>
       <c r="N64">
-        <v>1.66262476</v>
+        <v>1.65524774</v>
       </c>
       <c r="O64">
-        <v>0.332524952</v>
+        <v>0.331049548</v>
       </c>
       <c r="P64">
-        <v>1.330099808</v>
+        <v>1.324198192</v>
       </c>
       <c r="Q64">
-        <v>1.910099808</v>
+        <v>1.904198192</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1603243841644146</v>
+        <v>0.1631510998046569</v>
       </c>
       <c r="T64">
-        <v>1.771655799904753</v>
+        <v>1.815384191855999</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6835,7 +6835,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.635143782597415</v>
+        <v>4.561570071762535</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6843,22 +6843,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08823710692772306</v>
+        <v>0.08940214787296855</v>
       </c>
       <c r="C65">
-        <v>6.525418183940269</v>
+        <v>6.160520380112912</v>
       </c>
       <c r="D65">
-        <v>12.76961818394027</v>
+        <v>12.53812038011291</v>
       </c>
       <c r="E65">
-        <v>1.124199999999999</v>
+        <v>1.257599999999999</v>
       </c>
       <c r="F65">
-        <v>8.404199999999999</v>
+        <v>8.537599999999999</v>
       </c>
       <c r="G65">
         <v>2.16</v>
@@ -6879,45 +6879,45 @@
         <v>2.12</v>
       </c>
       <c r="M65">
-        <v>0.46475226</v>
+        <v>0.49347328</v>
       </c>
       <c r="N65">
-        <v>1.65524774</v>
+        <v>1.62652672</v>
       </c>
       <c r="O65">
-        <v>0.331049548</v>
+        <v>0.3253053440000001</v>
       </c>
       <c r="P65">
-        <v>1.324198192</v>
+        <v>1.301221376</v>
       </c>
       <c r="Q65">
-        <v>1.904198192</v>
+        <v>1.881221376</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1631510998046569</v>
+        <v>0.1661348552026904</v>
       </c>
       <c r="T65">
-        <v>1.815384191855999</v>
+        <v>1.861541938915648</v>
       </c>
       <c r="U65">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V65">
         <v>0.2</v>
       </c>
       <c r="W65">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y65">
-        <v>4.561570071762535</v>
+        <v>4.296078604296468</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6925,22 +6925,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08940214787296855</v>
+        <v>0.08930718881821402</v>
       </c>
       <c r="C66">
-        <v>6.160520380112912</v>
+        <v>6.045674433057531</v>
       </c>
       <c r="D66">
-        <v>12.53812038011291</v>
+        <v>12.55667443305753</v>
       </c>
       <c r="E66">
-        <v>1.257599999999999</v>
+        <v>1.390999999999999</v>
       </c>
       <c r="F66">
-        <v>8.537599999999999</v>
+        <v>8.670999999999999</v>
       </c>
       <c r="G66">
         <v>2.16</v>
@@ -6961,28 +6961,28 @@
         <v>2.12</v>
       </c>
       <c r="M66">
-        <v>0.49347328</v>
+        <v>0.5011838</v>
       </c>
       <c r="N66">
-        <v>1.62652672</v>
+        <v>1.6188162</v>
       </c>
       <c r="O66">
-        <v>0.3253053440000001</v>
+        <v>0.3237632400000001</v>
       </c>
       <c r="P66">
-        <v>1.301221376</v>
+        <v>1.29505296</v>
       </c>
       <c r="Q66">
-        <v>1.881221376</v>
+        <v>1.87505296</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1661348552026904</v>
+        <v>0.1692891109091829</v>
       </c>
       <c r="T66">
-        <v>1.861541938915648</v>
+        <v>1.910337271521563</v>
       </c>
       <c r="U66">
         <v>0.0578</v>
@@ -6999,7 +6999,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>4.296078604296468</v>
+        <v>4.229985087307291</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -7007,22 +7007,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08930718881821402</v>
+        <v>0.08921222976345951</v>
       </c>
       <c r="C67">
-        <v>6.045674433057531</v>
+        <v>5.930883480380016</v>
       </c>
       <c r="D67">
-        <v>12.55667443305753</v>
+        <v>12.57528348038002</v>
       </c>
       <c r="E67">
-        <v>1.390999999999999</v>
+        <v>1.524400000000001</v>
       </c>
       <c r="F67">
-        <v>8.670999999999999</v>
+        <v>8.804400000000001</v>
       </c>
       <c r="G67">
         <v>2.16</v>
@@ -7043,28 +7043,28 @@
         <v>2.12</v>
       </c>
       <c r="M67">
-        <v>0.5011838</v>
+        <v>0.5088943200000001</v>
       </c>
       <c r="N67">
-        <v>1.6188162</v>
+        <v>1.61110568</v>
       </c>
       <c r="O67">
-        <v>0.3237632400000001</v>
+        <v>0.322221136</v>
       </c>
       <c r="P67">
-        <v>1.29505296</v>
+        <v>1.288884544</v>
       </c>
       <c r="Q67">
-        <v>1.87505296</v>
+        <v>1.868884544</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1692891109091829</v>
+        <v>0.1726289110689986</v>
       </c>
       <c r="T67">
-        <v>1.910337271521563</v>
+        <v>1.962002917810179</v>
       </c>
       <c r="U67">
         <v>0.0578</v>
@@ -7081,7 +7081,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.229985087307291</v>
+        <v>4.165894404166272</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7089,22 +7089,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08921222976345951</v>
+        <v>0.08911727070870501</v>
       </c>
       <c r="C68">
-        <v>5.930883480380016</v>
+        <v>5.816147766949001</v>
       </c>
       <c r="D68">
-        <v>12.57528348038002</v>
+        <v>12.593947766949</v>
       </c>
       <c r="E68">
-        <v>1.524400000000001</v>
+        <v>1.657800000000001</v>
       </c>
       <c r="F68">
-        <v>8.804400000000001</v>
+        <v>8.937800000000001</v>
       </c>
       <c r="G68">
         <v>2.16</v>
@@ -7125,28 +7125,28 @@
         <v>2.12</v>
       </c>
       <c r="M68">
-        <v>0.5088943200000001</v>
+        <v>0.5166048400000001</v>
       </c>
       <c r="N68">
-        <v>1.61110568</v>
+        <v>1.60339516</v>
       </c>
       <c r="O68">
-        <v>0.322221136</v>
+        <v>0.320679032</v>
       </c>
       <c r="P68">
-        <v>1.288884544</v>
+        <v>1.282716128</v>
       </c>
       <c r="Q68">
-        <v>1.868884544</v>
+        <v>1.862716128</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1726289110689986</v>
+        <v>0.1761711233597121</v>
       </c>
       <c r="T68">
-        <v>1.962002917810179</v>
+        <v>2.016799815389014</v>
       </c>
       <c r="U68">
         <v>0.0578</v>
@@ -7163,7 +7163,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.165894404166272</v>
+        <v>4.10371687574588</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7171,22 +7171,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08911727070870501</v>
+        <v>0.08902231165395047</v>
       </c>
       <c r="C69">
-        <v>5.816147766949001</v>
+        <v>5.70146753908903</v>
       </c>
       <c r="D69">
-        <v>12.593947766949</v>
+        <v>12.61266753908903</v>
       </c>
       <c r="E69">
-        <v>1.657800000000001</v>
+        <v>1.791200000000001</v>
       </c>
       <c r="F69">
-        <v>8.937800000000001</v>
+        <v>9.071200000000001</v>
       </c>
       <c r="G69">
         <v>2.16</v>
@@ -7207,28 +7207,28 @@
         <v>2.12</v>
       </c>
       <c r="M69">
-        <v>0.5166048400000001</v>
+        <v>0.5243153600000001</v>
       </c>
       <c r="N69">
-        <v>1.60339516</v>
+        <v>1.59568464</v>
       </c>
       <c r="O69">
-        <v>0.320679032</v>
+        <v>0.319136928</v>
       </c>
       <c r="P69">
-        <v>1.282716128</v>
+        <v>1.276547712</v>
       </c>
       <c r="Q69">
-        <v>1.862716128</v>
+        <v>1.856547712</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1761711233597121</v>
+        <v>0.1799347239185952</v>
       </c>
       <c r="T69">
-        <v>2.016799815389014</v>
+        <v>2.075021519066525</v>
       </c>
       <c r="U69">
         <v>0.0578</v>
@@ -7245,7 +7245,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.10371687574588</v>
+        <v>4.04336809816138</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7253,22 +7253,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08902231165395047</v>
+        <v>0.09085935259919596</v>
       </c>
       <c r="C70">
-        <v>5.70146753908903</v>
+        <v>5.2155214540507</v>
       </c>
       <c r="D70">
-        <v>12.61266753908903</v>
+        <v>12.2601214540507</v>
       </c>
       <c r="E70">
-        <v>1.791200000000001</v>
+        <v>1.924600000000001</v>
       </c>
       <c r="F70">
-        <v>9.071200000000001</v>
+        <v>9.204600000000001</v>
       </c>
       <c r="G70">
         <v>2.16</v>
@@ -7289,45 +7289,45 @@
         <v>2.12</v>
       </c>
       <c r="M70">
-        <v>0.5243153600000001</v>
+        <v>0.56424198</v>
       </c>
       <c r="N70">
-        <v>1.59568464</v>
+        <v>1.55575802</v>
       </c>
       <c r="O70">
-        <v>0.319136928</v>
+        <v>0.311151604</v>
       </c>
       <c r="P70">
-        <v>1.276547712</v>
+        <v>1.244606416</v>
       </c>
       <c r="Q70">
-        <v>1.856547712</v>
+        <v>1.824606416</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1799347239185952</v>
+        <v>0.1839411374167612</v>
       </c>
       <c r="T70">
-        <v>2.075021519066525</v>
+        <v>2.136999461690974</v>
       </c>
       <c r="U70">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V70">
         <v>0.2</v>
       </c>
       <c r="W70">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y70">
-        <v>4.04336809816138</v>
+        <v>3.757253226709576</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7335,22 +7335,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09085935259919596</v>
+        <v>0.09079239354444145</v>
       </c>
       <c r="C71">
-        <v>5.2155214540507</v>
+        <v>5.094625106512138</v>
       </c>
       <c r="D71">
-        <v>12.2601214540507</v>
+        <v>12.27262510651214</v>
       </c>
       <c r="E71">
-        <v>1.924600000000001</v>
+        <v>2.058000000000001</v>
       </c>
       <c r="F71">
-        <v>9.204600000000001</v>
+        <v>9.338000000000001</v>
       </c>
       <c r="G71">
         <v>2.16</v>
@@ -7371,28 +7371,28 @@
         <v>2.12</v>
       </c>
       <c r="M71">
-        <v>0.56424198</v>
+        <v>0.5724194</v>
       </c>
       <c r="N71">
-        <v>1.55575802</v>
+        <v>1.5475806</v>
       </c>
       <c r="O71">
-        <v>0.311151604</v>
+        <v>0.3095161200000001</v>
       </c>
       <c r="P71">
-        <v>1.244606416</v>
+        <v>1.23806448</v>
       </c>
       <c r="Q71">
-        <v>1.824606416</v>
+        <v>1.81806448</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1839411374167612</v>
+        <v>0.1882146451481382</v>
       </c>
       <c r="T71">
-        <v>2.136999461690974</v>
+        <v>2.203109267157052</v>
       </c>
       <c r="U71">
         <v>0.0613</v>
@@ -7409,7 +7409,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.757253226709576</v>
+        <v>3.703578180613725</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7417,22 +7417,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09079239354444145</v>
+        <v>0.09072543448968695</v>
       </c>
       <c r="C72">
-        <v>5.094625106512138</v>
+        <v>4.973754289052554</v>
       </c>
       <c r="D72">
-        <v>12.27262510651214</v>
+        <v>12.28515428905255</v>
       </c>
       <c r="E72">
-        <v>2.058000000000001</v>
+        <v>2.191400000000001</v>
       </c>
       <c r="F72">
-        <v>9.338000000000001</v>
+        <v>9.471400000000001</v>
       </c>
       <c r="G72">
         <v>2.16</v>
@@ -7453,28 +7453,28 @@
         <v>2.12</v>
       </c>
       <c r="M72">
-        <v>0.5724194</v>
+        <v>0.58059682</v>
       </c>
       <c r="N72">
-        <v>1.5475806</v>
+        <v>1.53940318</v>
       </c>
       <c r="O72">
-        <v>0.3095161200000001</v>
+        <v>0.307880636</v>
       </c>
       <c r="P72">
-        <v>1.23806448</v>
+        <v>1.231522544</v>
       </c>
       <c r="Q72">
-        <v>1.81806448</v>
+        <v>1.811522544</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1882146451481382</v>
+        <v>0.1927828775506447</v>
       </c>
       <c r="T72">
-        <v>2.203109267157052</v>
+        <v>2.273778369551826</v>
       </c>
       <c r="U72">
         <v>0.0613</v>
@@ -7491,7 +7491,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.703578180613725</v>
+        <v>3.651415107647334</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7499,22 +7499,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09072543448968695</v>
+        <v>0.09065847543493241</v>
       </c>
       <c r="C73">
-        <v>4.973754289052556</v>
+        <v>4.852909079943208</v>
       </c>
       <c r="D73">
-        <v>12.28515428905255</v>
+        <v>12.29770907994321</v>
       </c>
       <c r="E73">
-        <v>2.191399999999999</v>
+        <v>2.324799999999999</v>
       </c>
       <c r="F73">
-        <v>9.471399999999999</v>
+        <v>9.604799999999999</v>
       </c>
       <c r="G73">
         <v>2.16</v>
@@ -7535,28 +7535,28 @@
         <v>2.12</v>
       </c>
       <c r="M73">
-        <v>0.5805968199999999</v>
+        <v>0.58877424</v>
       </c>
       <c r="N73">
-        <v>1.53940318</v>
+        <v>1.53122576</v>
       </c>
       <c r="O73">
-        <v>0.3078806360000001</v>
+        <v>0.306245152</v>
       </c>
       <c r="P73">
-        <v>1.231522544</v>
+        <v>1.224980608</v>
       </c>
       <c r="Q73">
-        <v>1.811522544</v>
+        <v>1.804980608</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1927828775506446</v>
+        <v>0.1976774122676158</v>
       </c>
       <c r="T73">
-        <v>2.273778369551825</v>
+        <v>2.349495264974796</v>
       </c>
       <c r="U73">
         <v>0.0613</v>
@@ -7573,7 +7573,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.651415107647335</v>
+        <v>3.60070100893001</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7581,22 +7581,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09065847543493241</v>
+        <v>0.0905915163801779</v>
       </c>
       <c r="C74">
-        <v>4.852909079943208</v>
+        <v>4.732089557775618</v>
       </c>
       <c r="D74">
-        <v>12.29770907994321</v>
+        <v>12.31028955777562</v>
       </c>
       <c r="E74">
-        <v>2.324799999999999</v>
+        <v>2.458199999999999</v>
       </c>
       <c r="F74">
-        <v>9.604799999999999</v>
+        <v>9.738199999999999</v>
       </c>
       <c r="G74">
         <v>2.16</v>
@@ -7617,28 +7617,28 @@
         <v>2.12</v>
       </c>
       <c r="M74">
-        <v>0.58877424</v>
+        <v>0.59695166</v>
       </c>
       <c r="N74">
-        <v>1.53122576</v>
+        <v>1.52304834</v>
       </c>
       <c r="O74">
-        <v>0.306245152</v>
+        <v>0.3046096680000001</v>
       </c>
       <c r="P74">
-        <v>1.224980608</v>
+        <v>1.218438672</v>
       </c>
       <c r="Q74">
-        <v>1.804980608</v>
+        <v>1.798438672</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1976774122676158</v>
+        <v>0.20293450511177</v>
       </c>
       <c r="T74">
-        <v>2.349495264974796</v>
+        <v>2.430820819317987</v>
       </c>
       <c r="U74">
         <v>0.0613</v>
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.60070100893001</v>
+        <v>3.551376337574805</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7663,22 +7663,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.0905915163801779</v>
+        <v>0.09052455732542339</v>
       </c>
       <c r="C75">
-        <v>4.732089557775618</v>
+        <v>4.611295801463253</v>
       </c>
       <c r="D75">
-        <v>12.31028955777562</v>
+        <v>12.32289580146325</v>
       </c>
       <c r="E75">
-        <v>2.458199999999999</v>
+        <v>2.591599999999999</v>
       </c>
       <c r="F75">
-        <v>9.738199999999999</v>
+        <v>9.871599999999999</v>
       </c>
       <c r="G75">
         <v>2.16</v>
@@ -7699,28 +7699,28 @@
         <v>2.12</v>
       </c>
       <c r="M75">
-        <v>0.59695166</v>
+        <v>0.60512908</v>
       </c>
       <c r="N75">
-        <v>1.52304834</v>
+        <v>1.51487092</v>
       </c>
       <c r="O75">
-        <v>0.3046096680000001</v>
+        <v>0.302974184</v>
       </c>
       <c r="P75">
-        <v>1.218438672</v>
+        <v>1.211896736</v>
       </c>
       <c r="Q75">
-        <v>1.798438672</v>
+        <v>1.791896736</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.20293450511177</v>
+        <v>0.2085959897131669</v>
       </c>
       <c r="T75">
-        <v>2.430820819317987</v>
+        <v>2.518402185533732</v>
       </c>
       <c r="U75">
         <v>0.0613</v>
@@ -7737,7 +7737,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.551376337574805</v>
+        <v>3.503384765445416</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7745,22 +7745,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09052455732542339</v>
+        <v>0.09213759827066889</v>
       </c>
       <c r="C76">
-        <v>4.611295801463253</v>
+        <v>4.181219648551959</v>
       </c>
       <c r="D76">
-        <v>12.32289580146325</v>
+        <v>12.02621964855196</v>
       </c>
       <c r="E76">
-        <v>2.591599999999999</v>
+        <v>2.724999999999999</v>
       </c>
       <c r="F76">
-        <v>9.871599999999999</v>
+        <v>10.005</v>
       </c>
       <c r="G76">
         <v>2.16</v>
@@ -7781,45 +7781,45 @@
         <v>2.12</v>
       </c>
       <c r="M76">
-        <v>0.60512908</v>
+        <v>0.6413205</v>
       </c>
       <c r="N76">
-        <v>1.51487092</v>
+        <v>1.4786795</v>
       </c>
       <c r="O76">
-        <v>0.302974184</v>
+        <v>0.2957359000000001</v>
       </c>
       <c r="P76">
-        <v>1.211896736</v>
+        <v>1.1829436</v>
       </c>
       <c r="Q76">
-        <v>1.791896736</v>
+        <v>1.7629436</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2085959897131669</v>
+        <v>0.2147103930826755</v>
       </c>
       <c r="T76">
-        <v>2.518402185533732</v>
+        <v>2.612990061046736</v>
       </c>
       <c r="U76">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V76">
         <v>0.2</v>
       </c>
       <c r="W76">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y76">
-        <v>3.503384765445416</v>
+        <v>3.30567945356495</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7827,22 +7827,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09213759827066889</v>
+        <v>0.09209303921591436</v>
       </c>
       <c r="C77">
-        <v>4.181219648551959</v>
+        <v>4.055823121837236</v>
       </c>
       <c r="D77">
-        <v>12.02621964855196</v>
+        <v>12.03422312183724</v>
       </c>
       <c r="E77">
-        <v>2.724999999999999</v>
+        <v>2.8584</v>
       </c>
       <c r="F77">
-        <v>10.005</v>
+        <v>10.1384</v>
       </c>
       <c r="G77">
         <v>2.16</v>
@@ -7863,28 +7863,28 @@
         <v>2.12</v>
       </c>
       <c r="M77">
-        <v>0.6413205</v>
+        <v>0.6498714400000001</v>
       </c>
       <c r="N77">
-        <v>1.4786795</v>
+        <v>1.47012856</v>
       </c>
       <c r="O77">
-        <v>0.2957359000000001</v>
+        <v>0.294025712</v>
       </c>
       <c r="P77">
-        <v>1.1829436</v>
+        <v>1.176102848</v>
       </c>
       <c r="Q77">
-        <v>1.7629436</v>
+        <v>1.756102848</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2147103930826755</v>
+        <v>0.2213343300663098</v>
       </c>
       <c r="T77">
-        <v>2.612990061046736</v>
+        <v>2.715460259519157</v>
       </c>
       <c r="U77">
         <v>0.0641</v>
@@ -7901,7 +7901,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.30567945356495</v>
+        <v>3.2621836712812</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7909,22 +7909,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09209303921591436</v>
+        <v>0.09204848016115985</v>
       </c>
       <c r="C78">
-        <v>4.055823121837236</v>
+        <v>3.930437254871622</v>
       </c>
       <c r="D78">
-        <v>12.03422312183724</v>
+        <v>12.04223725487162</v>
       </c>
       <c r="E78">
-        <v>2.8584</v>
+        <v>2.9918</v>
       </c>
       <c r="F78">
-        <v>10.1384</v>
+        <v>10.2718</v>
       </c>
       <c r="G78">
         <v>2.16</v>
@@ -7945,28 +7945,28 @@
         <v>2.12</v>
       </c>
       <c r="M78">
-        <v>0.6498714400000001</v>
+        <v>0.6584223800000001</v>
       </c>
       <c r="N78">
-        <v>1.47012856</v>
+        <v>1.46157762</v>
       </c>
       <c r="O78">
-        <v>0.294025712</v>
+        <v>0.292315524</v>
       </c>
       <c r="P78">
-        <v>1.176102848</v>
+        <v>1.169262096</v>
       </c>
       <c r="Q78">
-        <v>1.756102848</v>
+        <v>1.749262096</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2213343300663098</v>
+        <v>0.2285342615702602</v>
       </c>
       <c r="T78">
-        <v>2.715460259519157</v>
+        <v>2.826840910032658</v>
       </c>
       <c r="U78">
         <v>0.0641</v>
@@ -7983,7 +7983,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.2621836712812</v>
+        <v>3.219817649576249</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7991,22 +7991,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09204848016115985</v>
+        <v>0.09200392110640532</v>
       </c>
       <c r="C79">
-        <v>3.930437254871622</v>
+        <v>3.805062068965748</v>
       </c>
       <c r="D79">
-        <v>12.04223725487162</v>
+        <v>12.05026206896575</v>
       </c>
       <c r="E79">
-        <v>2.9918</v>
+        <v>3.1252</v>
       </c>
       <c r="F79">
-        <v>10.2718</v>
+        <v>10.4052</v>
       </c>
       <c r="G79">
         <v>2.16</v>
@@ -8027,28 +8027,28 @@
         <v>2.12</v>
       </c>
       <c r="M79">
-        <v>0.6584223800000001</v>
+        <v>0.6669733200000001</v>
       </c>
       <c r="N79">
-        <v>1.46157762</v>
+        <v>1.45302668</v>
       </c>
       <c r="O79">
-        <v>0.292315524</v>
+        <v>0.290605336</v>
       </c>
       <c r="P79">
-        <v>1.169262096</v>
+        <v>1.162421344</v>
       </c>
       <c r="Q79">
-        <v>1.749262096</v>
+        <v>1.742421344</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2285342615702602</v>
+        <v>0.2363887323018424</v>
       </c>
       <c r="T79">
-        <v>2.826840910032658</v>
+        <v>2.948347074229205</v>
       </c>
       <c r="U79">
         <v>0.0641</v>
@@ -8065,7 +8065,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.219817649576249</v>
+        <v>3.178537936120143</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8073,22 +8073,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09200392110640532</v>
+        <v>0.09195936205165081</v>
       </c>
       <c r="C80">
-        <v>3.805062068965748</v>
+        <v>3.679697585487064</v>
       </c>
       <c r="D80">
-        <v>12.05026206896575</v>
+        <v>12.05829758548706</v>
       </c>
       <c r="E80">
-        <v>3.1252</v>
+        <v>3.2586</v>
       </c>
       <c r="F80">
-        <v>10.4052</v>
+        <v>10.5386</v>
       </c>
       <c r="G80">
         <v>2.16</v>
@@ -8109,28 +8109,28 @@
         <v>2.12</v>
       </c>
       <c r="M80">
-        <v>0.6669733200000001</v>
+        <v>0.6755242600000001</v>
       </c>
       <c r="N80">
-        <v>1.45302668</v>
+        <v>1.44447574</v>
       </c>
       <c r="O80">
-        <v>0.290605336</v>
+        <v>0.288895148</v>
       </c>
       <c r="P80">
-        <v>1.162421344</v>
+        <v>1.155580592</v>
       </c>
       <c r="Q80">
-        <v>1.742421344</v>
+        <v>1.735580592</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2363887323018424</v>
+        <v>0.2449912478650039</v>
       </c>
       <c r="T80">
-        <v>2.948347074229205</v>
+        <v>3.081425254063518</v>
       </c>
       <c r="U80">
         <v>0.0641</v>
@@ -8147,7 +8147,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.178537936120143</v>
+        <v>3.138303278700901</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8155,22 +8155,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09195936205165081</v>
+        <v>0.09191480299689629</v>
       </c>
       <c r="C81">
-        <v>3.679697585487064</v>
+        <v>3.554343825860071</v>
       </c>
       <c r="D81">
-        <v>12.05829758548706</v>
+        <v>12.06634382586007</v>
       </c>
       <c r="E81">
-        <v>3.2586</v>
+        <v>3.392</v>
       </c>
       <c r="F81">
-        <v>10.5386</v>
+        <v>10.672</v>
       </c>
       <c r="G81">
         <v>2.16</v>
@@ -8191,28 +8191,28 @@
         <v>2.12</v>
       </c>
       <c r="M81">
-        <v>0.6755242600000001</v>
+        <v>0.6840752000000001</v>
       </c>
       <c r="N81">
-        <v>1.44447574</v>
+        <v>1.4359248</v>
       </c>
       <c r="O81">
-        <v>0.288895148</v>
+        <v>0.28718496</v>
       </c>
       <c r="P81">
-        <v>1.155580592</v>
+        <v>1.14873984</v>
       </c>
       <c r="Q81">
-        <v>1.735580592</v>
+        <v>1.72873984</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2449912478650039</v>
+        <v>0.2544540149844815</v>
       </c>
       <c r="T81">
-        <v>3.081425254063518</v>
+        <v>3.227811251881262</v>
       </c>
       <c r="U81">
         <v>0.0641</v>
@@ -8229,7 +8229,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.138303278700901</v>
+        <v>3.099074487717139</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8237,22 +8237,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09191480299689629</v>
+        <v>0.0918702439421418</v>
       </c>
       <c r="C82">
-        <v>3.554343825860071</v>
+        <v>3.429000811566473</v>
       </c>
       <c r="D82">
-        <v>12.06634382586007</v>
+        <v>12.07440081156647</v>
       </c>
       <c r="E82">
-        <v>3.392</v>
+        <v>3.5254</v>
       </c>
       <c r="F82">
-        <v>10.672</v>
+        <v>10.8054</v>
       </c>
       <c r="G82">
         <v>2.16</v>
@@ -8273,28 +8273,28 @@
         <v>2.12</v>
       </c>
       <c r="M82">
-        <v>0.6840752000000001</v>
+        <v>0.6926261400000001</v>
       </c>
       <c r="N82">
-        <v>1.4359248</v>
+        <v>1.42737386</v>
       </c>
       <c r="O82">
-        <v>0.28718496</v>
+        <v>0.285474772</v>
       </c>
       <c r="P82">
-        <v>1.14873984</v>
+        <v>1.141899088</v>
       </c>
       <c r="Q82">
-        <v>1.72873984</v>
+        <v>1.721899088</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2544540149844815</v>
+        <v>0.2649128628533779</v>
       </c>
       <c r="T82">
-        <v>3.227811251881262</v>
+        <v>3.389606302100875</v>
       </c>
       <c r="U82">
         <v>0.0641</v>
@@ -8311,7 +8311,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.099074487717139</v>
+        <v>3.060814308856434</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8319,22 +8319,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.0918702439421418</v>
+        <v>0.09182568488738727</v>
       </c>
       <c r="C83">
-        <v>3.429000811566473</v>
+        <v>3.303668564145417</v>
       </c>
       <c r="D83">
-        <v>12.07440081156647</v>
+        <v>12.08246856414542</v>
       </c>
       <c r="E83">
-        <v>3.5254</v>
+        <v>3.6588</v>
       </c>
       <c r="F83">
-        <v>10.8054</v>
+        <v>10.9388</v>
       </c>
       <c r="G83">
         <v>2.16</v>
@@ -8355,28 +8355,28 @@
         <v>2.12</v>
       </c>
       <c r="M83">
-        <v>0.6926261400000001</v>
+        <v>0.7011770800000001</v>
       </c>
       <c r="N83">
-        <v>1.42737386</v>
+        <v>1.41882292</v>
       </c>
       <c r="O83">
-        <v>0.285474772</v>
+        <v>0.283764584</v>
       </c>
       <c r="P83">
-        <v>1.141899088</v>
+        <v>1.135058336</v>
       </c>
       <c r="Q83">
-        <v>1.721899088</v>
+        <v>1.715058336</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2649128628533779</v>
+        <v>0.2765338049299293</v>
       </c>
       <c r="T83">
-        <v>3.389606302100875</v>
+        <v>3.569378580122666</v>
       </c>
       <c r="U83">
         <v>0.0641</v>
@@ -8393,7 +8393,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.060814308856434</v>
+        <v>3.023487305089892</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8401,22 +8401,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09182568488738727</v>
+        <v>0.09696032583263275</v>
       </c>
       <c r="C84">
-        <v>3.303668564145417</v>
+        <v>2.306488489001595</v>
       </c>
       <c r="D84">
-        <v>12.08246856414542</v>
+        <v>11.21868848900159</v>
       </c>
       <c r="E84">
-        <v>3.6588</v>
+        <v>3.7922</v>
       </c>
       <c r="F84">
-        <v>10.9388</v>
+        <v>11.0722</v>
       </c>
       <c r="G84">
         <v>2.16</v>
@@ -8437,45 +8437,45 @@
         <v>2.12</v>
       </c>
       <c r="M84">
-        <v>0.7011770800000001</v>
+        <v>0.7960911800000001</v>
       </c>
       <c r="N84">
-        <v>1.41882292</v>
+        <v>1.32390882</v>
       </c>
       <c r="O84">
-        <v>0.283764584</v>
+        <v>0.264781764</v>
       </c>
       <c r="P84">
-        <v>1.135058336</v>
+        <v>1.059127056</v>
       </c>
       <c r="Q84">
-        <v>1.715058336</v>
+        <v>1.639127056</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2765338049299293</v>
+        <v>0.2895219166625457</v>
       </c>
       <c r="T84">
-        <v>3.569378580122666</v>
+        <v>3.770300537911727</v>
       </c>
       <c r="U84">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V84">
         <v>0.2</v>
       </c>
       <c r="W84">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y84">
-        <v>3.023487305089892</v>
+        <v>2.66301154096444</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8483,22 +8483,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09696032583263275</v>
+        <v>0.09697816677787824</v>
       </c>
       <c r="C85">
-        <v>2.306488489001595</v>
+        <v>2.170302435118652</v>
       </c>
       <c r="D85">
-        <v>11.21868848900159</v>
+        <v>11.21590243511865</v>
       </c>
       <c r="E85">
-        <v>3.7922</v>
+        <v>3.9256</v>
       </c>
       <c r="F85">
-        <v>11.0722</v>
+        <v>11.2056</v>
       </c>
       <c r="G85">
         <v>2.16</v>
@@ -8519,28 +8519,28 @@
         <v>2.12</v>
       </c>
       <c r="M85">
-        <v>0.7960911800000001</v>
+        <v>0.8056826400000001</v>
       </c>
       <c r="N85">
-        <v>1.32390882</v>
+        <v>1.31431736</v>
       </c>
       <c r="O85">
-        <v>0.264781764</v>
+        <v>0.262863472</v>
       </c>
       <c r="P85">
-        <v>1.059127056</v>
+        <v>1.051453888</v>
       </c>
       <c r="Q85">
-        <v>1.639127056</v>
+        <v>1.631453888</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2895219166625457</v>
+        <v>0.3041335423617391</v>
       </c>
       <c r="T85">
-        <v>3.770300537911727</v>
+        <v>3.996337740424421</v>
       </c>
       <c r="U85">
         <v>0.07190000000000001</v>
@@ -8557,7 +8557,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.66301154096444</v>
+        <v>2.631309022619626</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8565,22 +8565,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09697816677787824</v>
+        <v>0.09699600772312374</v>
       </c>
       <c r="C86">
-        <v>2.170302435118654</v>
+        <v>2.034117764671763</v>
       </c>
       <c r="D86">
-        <v>11.21590243511865</v>
+        <v>11.21311776467176</v>
       </c>
       <c r="E86">
-        <v>3.925599999999998</v>
+        <v>4.059</v>
       </c>
       <c r="F86">
-        <v>11.2056</v>
+        <v>11.339</v>
       </c>
       <c r="G86">
         <v>2.16</v>
@@ -8601,28 +8601,28 @@
         <v>2.12</v>
       </c>
       <c r="M86">
-        <v>0.80568264</v>
+        <v>0.8152741000000001</v>
       </c>
       <c r="N86">
-        <v>1.31431736</v>
+        <v>1.3047259</v>
       </c>
       <c r="O86">
-        <v>0.262863472</v>
+        <v>0.26094518</v>
       </c>
       <c r="P86">
-        <v>1.051453888</v>
+        <v>1.04378072</v>
       </c>
       <c r="Q86">
-        <v>1.631453888</v>
+        <v>1.62378072</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.304133542361739</v>
+        <v>0.3206933848208248</v>
       </c>
       <c r="T86">
-        <v>3.996337740424419</v>
+        <v>4.252513236605472</v>
       </c>
       <c r="U86">
         <v>0.07190000000000001</v>
@@ -8639,7 +8639,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.631309022619626</v>
+        <v>2.600352445882924</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8647,22 +8647,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09699600772312374</v>
+        <v>0.09701384866836923</v>
       </c>
       <c r="C87">
-        <v>2.034117764671763</v>
+        <v>1.897934476630752</v>
       </c>
       <c r="D87">
-        <v>11.21311776467176</v>
+        <v>11.21033447663075</v>
       </c>
       <c r="E87">
-        <v>4.059</v>
+        <v>4.1924</v>
       </c>
       <c r="F87">
-        <v>11.339</v>
+        <v>11.4724</v>
       </c>
       <c r="G87">
         <v>2.16</v>
@@ -8683,28 +8683,28 @@
         <v>2.12</v>
       </c>
       <c r="M87">
-        <v>0.8152741000000001</v>
+        <v>0.8248655600000001</v>
       </c>
       <c r="N87">
-        <v>1.3047259</v>
+        <v>1.29513444</v>
       </c>
       <c r="O87">
-        <v>0.26094518</v>
+        <v>0.259026888</v>
       </c>
       <c r="P87">
-        <v>1.04378072</v>
+        <v>1.036107552</v>
       </c>
       <c r="Q87">
-        <v>1.62378072</v>
+        <v>1.616107552</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3206933848208248</v>
+        <v>0.3396189190597801</v>
       </c>
       <c r="T87">
-        <v>4.252513236605472</v>
+        <v>4.54528523224096</v>
       </c>
       <c r="U87">
         <v>0.07190000000000001</v>
@@ -8721,7 +8721,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.600352445882924</v>
+        <v>2.570115789535449</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8729,22 +8729,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.09701384866836923</v>
+        <v>0.09703168961361471</v>
       </c>
       <c r="C88">
-        <v>1.897934476630752</v>
+        <v>1.76175256996647</v>
       </c>
       <c r="D88">
-        <v>11.21033447663075</v>
+        <v>11.20755256996647</v>
       </c>
       <c r="E88">
-        <v>4.1924</v>
+        <v>4.3258</v>
       </c>
       <c r="F88">
-        <v>11.4724</v>
+        <v>11.6058</v>
       </c>
       <c r="G88">
         <v>2.16</v>
@@ -8765,28 +8765,28 @@
         <v>2.12</v>
       </c>
       <c r="M88">
-        <v>0.8248655600000001</v>
+        <v>0.8344570200000001</v>
       </c>
       <c r="N88">
-        <v>1.29513444</v>
+        <v>1.28554298</v>
       </c>
       <c r="O88">
-        <v>0.259026888</v>
+        <v>0.257108596</v>
       </c>
       <c r="P88">
-        <v>1.036107552</v>
+        <v>1.028434384</v>
       </c>
       <c r="Q88">
-        <v>1.616107552</v>
+        <v>1.608434384</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3396189190597801</v>
+        <v>0.3614560739508823</v>
       </c>
       <c r="T88">
-        <v>4.54528523224096</v>
+        <v>4.883099073358832</v>
       </c>
       <c r="U88">
         <v>0.07190000000000001</v>
@@ -8803,7 +8803,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.570115789535449</v>
+        <v>2.54057422873619</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8811,22 +8811,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.09703168961361471</v>
+        <v>0.09704953055886018</v>
       </c>
       <c r="C89">
-        <v>1.76175256996647</v>
+        <v>1.625572043650775</v>
       </c>
       <c r="D89">
-        <v>11.20755256996647</v>
+        <v>11.20477204365078</v>
       </c>
       <c r="E89">
-        <v>4.3258</v>
+        <v>4.4592</v>
       </c>
       <c r="F89">
-        <v>11.6058</v>
+        <v>11.7392</v>
       </c>
       <c r="G89">
         <v>2.16</v>
@@ -8847,28 +8847,28 @@
         <v>2.12</v>
       </c>
       <c r="M89">
-        <v>0.8344570200000001</v>
+        <v>0.8440484800000001</v>
       </c>
       <c r="N89">
-        <v>1.28554298</v>
+        <v>1.27595152</v>
       </c>
       <c r="O89">
-        <v>0.257108596</v>
+        <v>0.255190304</v>
       </c>
       <c r="P89">
-        <v>1.028434384</v>
+        <v>1.020761216</v>
       </c>
       <c r="Q89">
-        <v>1.608434384</v>
+        <v>1.600761216</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3614560739508823</v>
+        <v>0.3869327546571681</v>
       </c>
       <c r="T89">
-        <v>4.883099073358832</v>
+        <v>5.277215221329682</v>
       </c>
       <c r="U89">
         <v>0.07190000000000001</v>
@@ -8885,7 +8885,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.54057422873619</v>
+        <v>2.511704067046006</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8893,22 +8893,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.09704953055886018</v>
+        <v>0.09984417150410567</v>
       </c>
       <c r="C90">
-        <v>1.625572043650775</v>
+        <v>1.073021942014158</v>
       </c>
       <c r="D90">
-        <v>11.20477204365078</v>
+        <v>10.78562194201416</v>
       </c>
       <c r="E90">
-        <v>4.4592</v>
+        <v>4.5926</v>
       </c>
       <c r="F90">
-        <v>11.7392</v>
+        <v>11.8726</v>
       </c>
       <c r="G90">
         <v>2.16</v>
@@ -8929,45 +8929,45 @@
         <v>2.12</v>
       </c>
       <c r="M90">
-        <v>0.8440484800000001</v>
+        <v>0.8999430800000001</v>
       </c>
       <c r="N90">
-        <v>1.27595152</v>
+        <v>1.22005692</v>
       </c>
       <c r="O90">
-        <v>0.255190304</v>
+        <v>0.244011384</v>
       </c>
       <c r="P90">
-        <v>1.020761216</v>
+        <v>0.976045536</v>
       </c>
       <c r="Q90">
-        <v>1.600761216</v>
+        <v>1.556045536</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3869327546571681</v>
+        <v>0.4170415591282333</v>
       </c>
       <c r="T90">
-        <v>5.277215221329682</v>
+        <v>5.742988850749778</v>
       </c>
       <c r="U90">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V90">
         <v>0.2</v>
       </c>
       <c r="W90">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y90">
-        <v>2.511704067046006</v>
+        <v>2.355704540780512</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8975,22 +8975,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.09984417150410567</v>
+        <v>0.09989321244935115</v>
       </c>
       <c r="C91">
-        <v>1.073021942014158</v>
+        <v>0.9325464024978949</v>
       </c>
       <c r="D91">
-        <v>10.78562194201416</v>
+        <v>10.77854640249789</v>
       </c>
       <c r="E91">
-        <v>4.5926</v>
+        <v>4.726</v>
       </c>
       <c r="F91">
-        <v>11.8726</v>
+        <v>12.006</v>
       </c>
       <c r="G91">
         <v>2.16</v>
@@ -9011,28 +9011,28 @@
         <v>2.12</v>
       </c>
       <c r="M91">
-        <v>0.8999430800000001</v>
+        <v>0.9100548000000001</v>
       </c>
       <c r="N91">
-        <v>1.22005692</v>
+        <v>1.2099452</v>
       </c>
       <c r="O91">
-        <v>0.244011384</v>
+        <v>0.24198904</v>
       </c>
       <c r="P91">
-        <v>0.976045536</v>
+        <v>0.96795616</v>
       </c>
       <c r="Q91">
-        <v>1.556045536</v>
+        <v>1.54795616</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4170415591282333</v>
+        <v>0.4531721244935116</v>
       </c>
       <c r="T91">
-        <v>5.742988850749778</v>
+        <v>6.301917206053893</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -9049,7 +9049,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.355704540780512</v>
+        <v>2.329530045882951</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9057,22 +9057,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.09989321244935115</v>
+        <v>0.09994225339459664</v>
       </c>
       <c r="C92">
-        <v>0.9325464024978949</v>
+        <v>0.792080140228494</v>
       </c>
       <c r="D92">
-        <v>10.77854640249789</v>
+        <v>10.77148014022849</v>
       </c>
       <c r="E92">
-        <v>4.726</v>
+        <v>4.8594</v>
       </c>
       <c r="F92">
-        <v>12.006</v>
+        <v>12.1394</v>
       </c>
       <c r="G92">
         <v>2.16</v>
@@ -9093,28 +9093,28 @@
         <v>2.12</v>
       </c>
       <c r="M92">
-        <v>0.9100548000000001</v>
+        <v>0.9201665200000001</v>
       </c>
       <c r="N92">
-        <v>1.2099452</v>
+        <v>1.19983348</v>
       </c>
       <c r="O92">
-        <v>0.24198904</v>
+        <v>0.239966696</v>
       </c>
       <c r="P92">
-        <v>0.96795616</v>
+        <v>0.9598667840000001</v>
       </c>
       <c r="Q92">
-        <v>1.54795616</v>
+        <v>1.539866784</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4531721244935116</v>
+        <v>0.4973317043844072</v>
       </c>
       <c r="T92">
-        <v>6.301917206053893</v>
+        <v>6.985051862536701</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -9131,7 +9131,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.329530045882951</v>
+        <v>2.303930814609512</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9139,22 +9139,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.09994225339459664</v>
+        <v>0.09999129433984212</v>
       </c>
       <c r="C93">
-        <v>0.792080140228494</v>
+        <v>0.6516231369718195</v>
       </c>
       <c r="D93">
-        <v>10.77148014022849</v>
+        <v>10.76442313697182</v>
       </c>
       <c r="E93">
-        <v>4.8594</v>
+        <v>4.9928</v>
       </c>
       <c r="F93">
-        <v>12.1394</v>
+        <v>12.2728</v>
       </c>
       <c r="G93">
         <v>2.16</v>
@@ -9175,28 +9175,28 @@
         <v>2.12</v>
       </c>
       <c r="M93">
-        <v>0.9201665200000001</v>
+        <v>0.93027824</v>
       </c>
       <c r="N93">
-        <v>1.19983348</v>
+        <v>1.18972176</v>
       </c>
       <c r="O93">
-        <v>0.239966696</v>
+        <v>0.237944352</v>
       </c>
       <c r="P93">
-        <v>0.9598667840000001</v>
+        <v>0.9517774080000001</v>
       </c>
       <c r="Q93">
-        <v>1.539866784</v>
+        <v>1.531777408</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4973317043844072</v>
+        <v>0.5525311792480267</v>
       </c>
       <c r="T93">
-        <v>6.985051862536701</v>
+        <v>7.838970183140212</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -9213,7 +9213,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.303930814609512</v>
+        <v>2.278888088363757</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9221,22 +9221,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.09999129433984212</v>
+        <v>0.1000403352850876</v>
       </c>
       <c r="C94">
-        <v>0.6516231369718195</v>
+        <v>0.5111753745414873</v>
       </c>
       <c r="D94">
-        <v>10.76442313697182</v>
+        <v>10.75737537454149</v>
       </c>
       <c r="E94">
-        <v>4.9928</v>
+        <v>5.1262</v>
       </c>
       <c r="F94">
-        <v>12.2728</v>
+        <v>12.4062</v>
       </c>
       <c r="G94">
         <v>2.16</v>
@@ -9257,28 +9257,28 @@
         <v>2.12</v>
       </c>
       <c r="M94">
-        <v>0.93027824</v>
+        <v>0.9403899600000001</v>
       </c>
       <c r="N94">
-        <v>1.18972176</v>
+        <v>1.17961004</v>
       </c>
       <c r="O94">
-        <v>0.237944352</v>
+        <v>0.235922008</v>
       </c>
       <c r="P94">
-        <v>0.9517774080000001</v>
+        <v>0.9436880320000001</v>
       </c>
       <c r="Q94">
-        <v>1.531777408</v>
+        <v>1.523688032</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5525311792480267</v>
+        <v>0.6235019326441089</v>
       </c>
       <c r="T94">
-        <v>7.838970183140212</v>
+        <v>8.936865166773295</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9295,7 +9295,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.278888088363757</v>
+        <v>2.254383915370598</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9303,22 +9303,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1000403352850876</v>
+        <v>0.1000893762303331</v>
       </c>
       <c r="C95">
-        <v>0.5111753745414873</v>
+        <v>0.3707368347987021</v>
       </c>
       <c r="D95">
-        <v>10.75737537454149</v>
+        <v>10.7503368347987</v>
       </c>
       <c r="E95">
-        <v>5.1262</v>
+        <v>5.2596</v>
       </c>
       <c r="F95">
-        <v>12.4062</v>
+        <v>12.5396</v>
       </c>
       <c r="G95">
         <v>2.16</v>
@@ -9339,28 +9339,28 @@
         <v>2.12</v>
       </c>
       <c r="M95">
-        <v>0.9403899600000001</v>
+        <v>0.9505016800000001</v>
       </c>
       <c r="N95">
-        <v>1.17961004</v>
+        <v>1.16949832</v>
       </c>
       <c r="O95">
-        <v>0.235922008</v>
+        <v>0.233899664</v>
       </c>
       <c r="P95">
-        <v>0.9436880320000001</v>
+        <v>0.935598656</v>
       </c>
       <c r="Q95">
-        <v>1.523688032</v>
+        <v>1.515598656</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6235019326441089</v>
+        <v>0.7181296038388852</v>
       </c>
       <c r="T95">
-        <v>8.936865166773295</v>
+        <v>10.40072514495074</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9377,7 +9377,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.254383915370598</v>
+        <v>2.230401107760272</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9385,22 +9385,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1000893762303331</v>
+        <v>0.1001384171755786</v>
       </c>
       <c r="C96">
-        <v>0.3707368347987021</v>
+        <v>0.2303074996521133</v>
       </c>
       <c r="D96">
-        <v>10.7503368347987</v>
+        <v>10.74330749965211</v>
       </c>
       <c r="E96">
-        <v>5.2596</v>
+        <v>5.393</v>
       </c>
       <c r="F96">
-        <v>12.5396</v>
+        <v>12.673</v>
       </c>
       <c r="G96">
         <v>2.16</v>
@@ -9421,28 +9421,28 @@
         <v>2.12</v>
       </c>
       <c r="M96">
-        <v>0.9505016800000001</v>
+        <v>0.9606134000000001</v>
       </c>
       <c r="N96">
-        <v>1.16949832</v>
+        <v>1.1593866</v>
       </c>
       <c r="O96">
-        <v>0.233899664</v>
+        <v>0.23187732</v>
       </c>
       <c r="P96">
-        <v>0.935598656</v>
+        <v>0.92750928</v>
       </c>
       <c r="Q96">
-        <v>1.515598656</v>
+        <v>1.50750928</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7181296038388852</v>
+        <v>0.8506083435115726</v>
       </c>
       <c r="T96">
-        <v>10.40072514495074</v>
+        <v>12.45012911439917</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9459,7 +9459,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.230401107760272</v>
+        <v>2.206923201362796</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9467,22 +9467,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1001384171755786</v>
+        <v>0.1001874581208241</v>
       </c>
       <c r="C97">
-        <v>0.2303074996521133</v>
+        <v>0.08988735105766743</v>
       </c>
       <c r="D97">
-        <v>10.74330749965211</v>
+        <v>10.73628735105767</v>
       </c>
       <c r="E97">
-        <v>5.393</v>
+        <v>5.5264</v>
       </c>
       <c r="F97">
-        <v>12.673</v>
+        <v>12.8064</v>
       </c>
       <c r="G97">
         <v>2.16</v>
@@ -9503,28 +9503,28 @@
         <v>2.12</v>
       </c>
       <c r="M97">
-        <v>0.9606134000000001</v>
+        <v>0.9707251200000001</v>
       </c>
       <c r="N97">
-        <v>1.1593866</v>
+        <v>1.14927488</v>
       </c>
       <c r="O97">
-        <v>0.23187732</v>
+        <v>0.229854976</v>
       </c>
       <c r="P97">
-        <v>0.92750928</v>
+        <v>0.9194199040000001</v>
       </c>
       <c r="Q97">
-        <v>1.50750928</v>
+        <v>1.499419904</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8506083435115726</v>
+        <v>1.049326453020603</v>
       </c>
       <c r="T97">
-        <v>12.45012911439917</v>
+        <v>15.52423506857181</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9541,7 +9541,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.206923201362796</v>
+        <v>2.183934418015267</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9549,22 +9549,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1001874581208241</v>
+        <v>0.1002364990660696</v>
       </c>
       <c r="C98">
-        <v>0.08988735105766743</v>
+        <v>-0.05052362898156559</v>
       </c>
       <c r="D98">
-        <v>10.73628735105767</v>
+        <v>10.72927637101843</v>
       </c>
       <c r="E98">
-        <v>5.5264</v>
+        <v>5.6598</v>
       </c>
       <c r="F98">
-        <v>12.8064</v>
+        <v>12.9398</v>
       </c>
       <c r="G98">
         <v>2.16</v>
@@ -9585,28 +9585,28 @@
         <v>2.12</v>
       </c>
       <c r="M98">
-        <v>0.9707251200000001</v>
+        <v>0.98083684</v>
       </c>
       <c r="N98">
-        <v>1.14927488</v>
+        <v>1.13916316</v>
       </c>
       <c r="O98">
-        <v>0.229854976</v>
+        <v>0.227832632</v>
       </c>
       <c r="P98">
-        <v>0.9194199040000001</v>
+        <v>0.911330528</v>
       </c>
       <c r="Q98">
-        <v>1.499419904</v>
+        <v>1.491330528</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.049326453020601</v>
+        <v>1.380523302202317</v>
       </c>
       <c r="T98">
-        <v>15.52423506857177</v>
+        <v>20.64774499219282</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9623,7 +9623,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.183934418015267</v>
+        <v>2.161419630200677</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9631,22 +9631,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1002364990660696</v>
+        <v>0.100285540011315</v>
       </c>
       <c r="C99">
-        <v>-0.05052362898156559</v>
+        <v>-0.1909254584155384</v>
       </c>
       <c r="D99">
-        <v>10.72927637101843</v>
+        <v>10.72227454158446</v>
       </c>
       <c r="E99">
-        <v>5.6598</v>
+        <v>5.7932</v>
       </c>
       <c r="F99">
-        <v>12.9398</v>
+        <v>13.0732</v>
       </c>
       <c r="G99">
         <v>2.16</v>
@@ -9667,28 +9667,28 @@
         <v>2.12</v>
       </c>
       <c r="M99">
-        <v>0.98083684</v>
+        <v>0.9909485600000001</v>
       </c>
       <c r="N99">
-        <v>1.13916316</v>
+        <v>1.12905144</v>
       </c>
       <c r="O99">
-        <v>0.227832632</v>
+        <v>0.225810288</v>
       </c>
       <c r="P99">
-        <v>0.911330528</v>
+        <v>0.903241152</v>
       </c>
       <c r="Q99">
-        <v>1.491330528</v>
+        <v>1.483241152</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.380523302202317</v>
+        <v>2.042917000565749</v>
       </c>
       <c r="T99">
-        <v>20.64774499219282</v>
+        <v>30.89476483943491</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9705,7 +9705,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.161419630200677</v>
+        <v>2.13936432785169</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9713,22 +9713,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.100285540011315</v>
+        <v>0.1003345809565605</v>
       </c>
       <c r="C100">
-        <v>-0.1909254584155384</v>
+        <v>-0.3313181551473772</v>
       </c>
       <c r="D100">
-        <v>10.72227454158446</v>
+        <v>10.71528184485262</v>
       </c>
       <c r="E100">
-        <v>5.7932</v>
+        <v>5.9266</v>
       </c>
       <c r="F100">
-        <v>13.0732</v>
+        <v>13.2066</v>
       </c>
       <c r="G100">
         <v>2.16</v>
@@ -9749,28 +9749,28 @@
         <v>2.12</v>
       </c>
       <c r="M100">
-        <v>0.9909485600000001</v>
+        <v>1.00106028</v>
       </c>
       <c r="N100">
-        <v>1.12905144</v>
+        <v>1.11893972</v>
       </c>
       <c r="O100">
-        <v>0.225810288</v>
+        <v>0.223787944</v>
       </c>
       <c r="P100">
-        <v>0.903241152</v>
+        <v>0.895151776</v>
       </c>
       <c r="Q100">
-        <v>1.483241152</v>
+        <v>1.475151776</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.042917000565749</v>
+        <v>4.030098095656047</v>
       </c>
       <c r="T100">
-        <v>30.89476483943491</v>
+        <v>61.63582438116118</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9787,91 +9787,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.13936432785169</v>
+        <v>2.117754587166319</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1003345809565605</v>
-      </c>
-      <c r="C101">
-        <v>-0.3313181551473772</v>
-      </c>
-      <c r="D101">
-        <v>10.71528184485262</v>
-      </c>
-      <c r="E101">
-        <v>5.9266</v>
-      </c>
-      <c r="F101">
-        <v>13.2066</v>
-      </c>
-      <c r="G101">
-        <v>2.16</v>
-      </c>
-      <c r="H101">
-        <v>6.06</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>2.7</v>
-      </c>
-      <c r="K101">
-        <v>0.5800000000000001</v>
-      </c>
-      <c r="L101">
-        <v>2.12</v>
-      </c>
-      <c r="M101">
-        <v>1.00106028</v>
-      </c>
-      <c r="N101">
-        <v>1.11893972</v>
-      </c>
-      <c r="O101">
-        <v>0.223787944</v>
-      </c>
-      <c r="P101">
-        <v>0.895151776</v>
-      </c>
-      <c r="Q101">
-        <v>1.475151776</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.030098095656047</v>
-      </c>
-      <c r="T101">
-        <v>61.63582438116118</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.2</v>
-      </c>
-      <c r="W101">
-        <v>0.06064000000000001</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.117754587166319</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
